--- a/timetables/1st Sem TIME TABLE 2026-2027_1.1.xlsx
+++ b/timetables/1st Sem TIME TABLE 2026-2027_1.1.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saranneralla/Documents/Documents-Saran-MacBook-Air/timetable-analytics/timetables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B6AE04-3506-D941-B12D-B4C338B6E24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A0EDFB-1602-6843-B12A-B9CA800FA27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="23" r:id="rId1"/>
     <sheet name="Timetable_Final" sheetId="25" r:id="rId2"/>
     <sheet name="Faculty_Workload_Summary" sheetId="29" r:id="rId3"/>
     <sheet name="Faculty_Workload_Department_Wis" sheetId="76" r:id="rId4"/>
+    <sheet name="Lab Sheets Summary" sheetId="77" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Faculty_Workload_Department_Wis!$A$1:$K$78</definedName>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="1005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="1046">
   <si>
     <t>A-301,302</t>
   </si>
@@ -14627,12 +14628,184 @@
   <si>
     <t>Not Specified</t>
   </si>
+  <si>
+    <t>Lab Name</t>
+  </si>
+  <si>
+    <t>Branches</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Allotted</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Extra</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>G-304, G-305, G-302, G-303, G-405</t>
+  </si>
+  <si>
+    <t>CSE-1 -&gt; G-304, G-305, G-302, G-303, G-405 -&gt; NOT ALLOTTED
+CSE-2 -&gt; G-304, G-305, G-302, G-303, G-405 -&gt; NOT ALLOTTED
+CSE(AI&amp;ML)-1 -&gt; G-304, G-305, G-302, G-303, G-405 -&gt; NOT ALLOTTED
+CSE(AI&amp;ML)-2 -&gt; G-304, G-305, G-302, G-303, G-405 -&gt; NOT ALLOTTED
+CSE (CS &amp; DS) -&gt; G-304, G-305, G-302, G-303, G-405 -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: CSE-1, CSE-2, CSE(AI&amp;ML)-1, CSE(AI&amp;ML)-2, CSE (CS &amp; DS)</t>
+  </si>
+  <si>
+    <t>CSE-1 -&gt; PHY LAB -&gt; NOT ALLOTTED
+CSE-2 -&gt; PHY LAB -&gt; NOT ALLOTTED
+CSE(AI&amp;ML)-1 -&gt; PHY LAB -&gt; NOT ALLOTTED
+CSE(AI&amp;ML)-2 -&gt; PHY LAB -&gt; NOT ALLOTTED
+CSE (CS &amp; DS) -&gt; PHY LAB -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: CSE-1 (2), CSE-2 (2), CSE(AI&amp;ML)-1 (2), CSE(AI&amp;ML)-2 (2), CSE (CS &amp; DS) (2)</t>
+  </si>
+  <si>
+    <t>COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302</t>
+  </si>
+  <si>
+    <t>CSE-1 -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+CSE-2 -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+CSE(AI&amp;ML)-1 -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+CSE(AI&amp;ML)-2 -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+CSE (CS &amp; DS) -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+ECE-1 -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+ECE-2 -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+ECE-3 -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+MECH -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+EEE -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+CIVIL -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+CHEMICAL -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED
+MECH-ROBOTICS -&gt; COMP. LAB-1, COMP. LAB-2, C-208, COMP. LAB-3, A-301,302 -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: CSE-1 (2), CSE-2 (2), CSE(AI&amp;ML)-1 (2), CSE(AI&amp;ML)-2 (2), CSE (CS &amp; DS) (2), ECE-1 (2), ECE-2 (2), ECE-3, MECH (2), EEE, CIVIL, CHEMICAL, MECH-ROBOTICS</t>
+  </si>
+  <si>
+    <t>COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1</t>
+  </si>
+  <si>
+    <t>CSE-1 -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+CSE-2 -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+CSE(AI&amp;ML)-1 -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+CSE(AI&amp;ML)-2 -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+CSE (CS &amp; DS) -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+ECE-1 -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+ECE-2 -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+ECE-3 -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+MECH -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+EEE -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+CIVIL -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+CHEMICAL -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED
+MECH-ROBOTICS -&gt; COMP. LAB-2, A-303,304, COMP. LAB-3, A-301,302, COMP. LAB-1 -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>CSE-1 -&gt; COMP. LAB-3 -&gt; NOT ALLOTTED
+CSE-2 -&gt; COMP. LAB-3 -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: CSE-1 (2), CSE-2 (2)</t>
+  </si>
+  <si>
+    <t>CSE(AI&amp;ML)-1 -&gt; COMP. LAB-1, COMP. LAB-3 -&gt; NOT ALLOTTED
+CSE(AI&amp;ML)-2 -&gt; COMP. LAB-1, COMP. LAB-3 -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: CSE(AI&amp;ML)-1 (2), CSE(AI&amp;ML)-2 (2)</t>
+  </si>
+  <si>
+    <t>CSE (CS &amp; DS) -&gt; COMP. LAB-3 -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: CSE (CS &amp; DS)</t>
+  </si>
+  <si>
+    <t>ECE-1 -&gt; CHEM. LAB. -&gt; NOT ALLOTTED
+ECE-2 -&gt; CHEM. LAB. -&gt; NOT ALLOTTED
+ECE-3 -&gt; CHEM. LAB. -&gt; NOT ALLOTTED
+EEE -&gt; CHEM. LAB. -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: ECE-1 (4), ECE-2 (4), ECE-3 (2), EEE (2)</t>
+  </si>
+  <si>
+    <t>ECE-1 -&gt; A-406 -&gt; NOT ALLOTTED
+ECE-2 -&gt; A-406 -&gt; NOT ALLOTTED
+ECE-3 -&gt; A-406 -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: ECE-1 (4), ECE-2 (4), ECE-3 (2)</t>
+  </si>
+  <si>
+    <t>ECE-1 -&gt; COMP. LAB-4 -&gt; NOT ALLOTTED
+ECE-2 -&gt; COMP. LAB-4 -&gt; NOT ALLOTTED
+ECE-3 -&gt; COMP. LAB-4 -&gt; NOT ALLOTTED
+MECH -&gt; COMP. LAB-4 -&gt; NOT ALLOTTED
+EEE -&gt; COMP. LAB-4 -&gt; NOT ALLOTTED
+CIVIL -&gt; COMP. LAB-4 -&gt; NOT ALLOTTED
+CHEMICAL -&gt; COMP. LAB-4 -&gt; NOT ALLOTTED
+MECH-ROBOTICS -&gt; COMP. LAB-4 -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: ECE-1 (2), ECE-2 (2), ECE-3, MECH (2), EEE, CIVIL, CHEMICAL, MECH-ROBOTICS</t>
+  </si>
+  <si>
+    <t>MECH -&gt; GVPCE CHEM. LAB. -&gt; NOT ALLOTTED
+CIVIL -&gt; GVPCE CHEM. LAB. -&gt; NOT ALLOTTED
+MECH-ROBOTICS -&gt; GVPCE CHEM. LAB. -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: MECH (2), CIVIL, MECH-ROBOTICS</t>
+  </si>
+  <si>
+    <t>MECH -&gt; GVPCE MECH. LAB -&gt; NOT ALLOTTED
+MECH-ROBOTICS -&gt; GVPCE MECH. LAB -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: MECH (2), MECH-ROBOTICS</t>
+  </si>
+  <si>
+    <t>EEE -&gt; E-319 -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: EEE (2)</t>
+  </si>
+  <si>
+    <t>CIVIL -&gt; GVPCE SUR. LAB -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: CIVIL</t>
+  </si>
+  <si>
+    <t>CHEMICAL -&gt; GVPCE CHEM. LAB. -&gt; NOT ALLOTTED</t>
+  </si>
+  <si>
+    <t>Not allotted: CHEMICAL</t>
+  </si>
+  <si>
+    <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>Remaining not allotted: 112</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14755,6 +14928,27 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="56">
@@ -15224,7 +15418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -15493,261 +15687,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="36" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="40" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="36" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="40" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="41" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="44" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="45" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="46" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="42" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="43" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="48" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="54" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="55" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="50" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="51" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="48" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="49" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="50" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="51" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="49" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="55" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="53" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="49" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="45" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="42" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="39" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="52" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="44" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="43" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -15763,6 +15702,282 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="43" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="42" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="52" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="46" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="49" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="50" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="51" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="45" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="54" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="44" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="48" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="49" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="39" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="48" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="49" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="55" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="55" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="53" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="50" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="51" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="41" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="42" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="43" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="44" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="45" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="40" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="40" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -49533,10 +49748,10 @@
       <c r="B2" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="135" t="s">
+      <c r="C2" s="174" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="94"/>
+      <c r="D2" s="110"/>
       <c r="E2" s="25" t="s">
         <v>169</v>
       </c>
@@ -49549,35 +49764,35 @@
       <c r="H2" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="I2" s="136" t="s">
+      <c r="I2" s="175" t="s">
         <v>176</v>
       </c>
-      <c r="J2" s="94"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="116" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="106" t="s">
+      <c r="C3" s="176" t="s">
         <v>180</v>
       </c>
-      <c r="D3" s="115" t="s">
+      <c r="D3" s="150" t="s">
         <v>181</v>
       </c>
       <c r="E3" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F3" s="140" t="s">
+      <c r="F3" s="172" t="s">
         <v>183</v>
       </c>
-      <c r="G3" s="95"/>
+      <c r="G3" s="105"/>
       <c r="H3" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I3" s="108" t="s">
+      <c r="I3" s="102" t="s">
         <v>186</v>
       </c>
       <c r="J3" s="29" t="s">
@@ -49585,15 +49800,15 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="97"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
       <c r="J4" s="30" t="s">
         <v>200</v>
       </c>
@@ -49614,10 +49829,10 @@
       <c r="E5" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="F5" s="109" t="s">
+      <c r="F5" s="130" t="s">
         <v>209</v>
       </c>
-      <c r="G5" s="94"/>
+      <c r="G5" s="110"/>
       <c r="H5" s="25" t="s">
         <v>175</v>
       </c>
@@ -49661,29 +49876,29 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="96" t="s">
+      <c r="A7" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="116" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="103" t="s">
+      <c r="C7" s="104" t="s">
         <v>225</v>
       </c>
-      <c r="D7" s="95"/>
+      <c r="D7" s="105"/>
       <c r="E7" s="100" t="s">
         <v>169</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="G7" s="137" t="s">
+      <c r="G7" s="163" t="s">
         <v>227</v>
       </c>
       <c r="H7" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I7" s="115" t="s">
+      <c r="I7" s="150" t="s">
         <v>228</v>
       </c>
       <c r="J7" s="36" t="s">
@@ -49691,17 +49906,17 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="97"/>
-      <c r="B8" s="97"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="97"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="101"/>
       <c r="F8" s="29" t="s">
         <v>232</v>
       </c>
-      <c r="G8" s="97"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
       <c r="J8" s="33" t="s">
         <v>214</v>
       </c>
@@ -49722,17 +49937,17 @@
       <c r="E9" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="F9" s="109" t="s">
+      <c r="F9" s="130" t="s">
         <v>239</v>
       </c>
-      <c r="G9" s="94"/>
+      <c r="G9" s="110"/>
       <c r="H9" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="I9" s="138" t="s">
+      <c r="I9" s="114" t="s">
         <v>242</v>
       </c>
-      <c r="J9" s="94"/>
+      <c r="J9" s="110"/>
     </row>
     <row r="10" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
@@ -49741,10 +49956,10 @@
       <c r="B10" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="141" t="s">
+      <c r="C10" s="173" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="94"/>
+      <c r="D10" s="110"/>
       <c r="E10" s="25" t="s">
         <v>169</v>
       </c>
@@ -49757,37 +49972,37 @@
       <c r="H10" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="I10" s="139" t="s">
+      <c r="I10" s="113" t="s">
         <v>267</v>
       </c>
-      <c r="J10" s="94"/>
+      <c r="J10" s="110"/>
     </row>
     <row r="11" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="116" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="171" t="s">
         <v>270</v>
       </c>
-      <c r="D11" s="98" t="s">
+      <c r="D11" s="112" t="s">
         <v>275</v>
       </c>
       <c r="E11" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F11" s="108" t="s">
+      <c r="F11" s="102" t="s">
         <v>278</v>
       </c>
-      <c r="G11" s="99" t="s">
+      <c r="G11" s="169" t="s">
         <v>281</v>
       </c>
       <c r="H11" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I11" s="102" t="s">
+      <c r="I11" s="170" t="s">
         <v>284</v>
       </c>
       <c r="J11" s="41" t="s">
@@ -49795,45 +50010,45 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="97"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="97"/>
-      <c r="G12" s="97"/>
-      <c r="H12" s="97"/>
-      <c r="I12" s="97"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="101"/>
       <c r="J12" s="30" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="116" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="98" t="s">
+      <c r="C13" s="112" t="s">
         <v>289</v>
       </c>
-      <c r="D13" s="99" t="s">
+      <c r="D13" s="169" t="s">
         <v>290</v>
       </c>
       <c r="E13" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F13" s="101" t="s">
+      <c r="F13" s="171" t="s">
         <v>293</v>
       </c>
-      <c r="G13" s="102" t="s">
+      <c r="G13" s="170" t="s">
         <v>294</v>
       </c>
       <c r="H13" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I13" s="98" t="s">
+      <c r="I13" s="112" t="s">
         <v>297</v>
       </c>
       <c r="J13" s="36" t="s">
@@ -49841,27 +50056,27 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="97"/>
-      <c r="B14" s="97"/>
-      <c r="C14" s="97"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="97"/>
-      <c r="F14" s="97"/>
-      <c r="G14" s="97"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="97"/>
+      <c r="A14" s="101"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="101"/>
       <c r="J14" s="33" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="96" t="s">
+      <c r="B15" s="116" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="101" t="s">
+      <c r="C15" s="171" t="s">
         <v>300</v>
       </c>
       <c r="D15" s="30" t="s">
@@ -49870,33 +50085,33 @@
       <c r="E15" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F15" s="103" t="s">
+      <c r="F15" s="104" t="s">
         <v>304</v>
       </c>
-      <c r="G15" s="95"/>
+      <c r="G15" s="105"/>
       <c r="H15" s="100" t="s">
         <v>175</v>
       </c>
       <c r="I15" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="J15" s="96"/>
+      <c r="J15" s="116"/>
     </row>
     <row r="16" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="97"/>
-      <c r="B16" s="97"/>
-      <c r="C16" s="97"/>
+      <c r="A16" s="101"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="101"/>
       <c r="D16" s="41" t="s">
         <v>318</v>
       </c>
-      <c r="E16" s="97"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="97"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="101"/>
       <c r="I16" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="J16" s="97"/>
+      <c r="J16" s="101"/>
     </row>
     <row r="17" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
@@ -49931,25 +50146,25 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="96" t="s">
+      <c r="A18" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="B18" s="96" t="s">
+      <c r="B18" s="116" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="106" t="s">
+      <c r="C18" s="176" t="s">
         <v>340</v>
       </c>
-      <c r="D18" s="98" t="s">
+      <c r="D18" s="112" t="s">
         <v>341</v>
       </c>
       <c r="E18" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F18" s="107" t="s">
+      <c r="F18" s="187" t="s">
         <v>342</v>
       </c>
-      <c r="G18" s="108" t="s">
+      <c r="G18" s="102" t="s">
         <v>343</v>
       </c>
       <c r="H18" s="100" t="s">
@@ -49958,39 +50173,39 @@
       <c r="I18" s="46" t="s">
         <v>346</v>
       </c>
-      <c r="J18" s="101" t="s">
+      <c r="J18" s="171" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="97"/>
-      <c r="B19" s="97"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
-      <c r="H19" s="97"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="101"/>
+      <c r="G19" s="101"/>
+      <c r="H19" s="101"/>
       <c r="I19" s="48" t="s">
         <v>352</v>
       </c>
-      <c r="J19" s="97"/>
+      <c r="J19" s="101"/>
     </row>
     <row r="20" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="96" t="s">
+      <c r="B20" s="116" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="111" t="s">
+      <c r="C20" s="143" t="s">
         <v>354</v>
       </c>
-      <c r="D20" s="94"/>
+      <c r="D20" s="110"/>
       <c r="E20" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="108" t="s">
+      <c r="F20" s="102" t="s">
         <v>358</v>
       </c>
       <c r="G20" s="49" t="s">
@@ -49999,44 +50214,44 @@
       <c r="H20" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I20" s="109" t="s">
+      <c r="I20" s="130" t="s">
         <v>361</v>
       </c>
-      <c r="J20" s="94"/>
+      <c r="J20" s="110"/>
     </row>
     <row r="21" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="97"/>
-      <c r="B21" s="97"/>
-      <c r="C21" s="112" t="s">
+      <c r="A21" s="101"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="182" t="s">
         <v>365</v>
       </c>
-      <c r="D21" s="94"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="97"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="101"/>
       <c r="G21" s="50" t="s">
         <v>366</v>
       </c>
-      <c r="H21" s="97"/>
-      <c r="I21" s="110" t="s">
+      <c r="H21" s="101"/>
+      <c r="I21" s="188" t="s">
         <v>367</v>
       </c>
-      <c r="J21" s="94"/>
+      <c r="J21" s="110"/>
     </row>
     <row r="22" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B22" s="96" t="s">
+      <c r="B22" s="116" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="113" t="s">
+      <c r="C22" s="185" t="s">
         <v>368</v>
       </c>
-      <c r="D22" s="94"/>
+      <c r="D22" s="110"/>
       <c r="E22" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F22" s="101" t="s">
+      <c r="F22" s="171" t="s">
         <v>369</v>
       </c>
       <c r="G22" s="51" t="s">
@@ -50045,137 +50260,137 @@
       <c r="H22" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I22" s="114" t="s">
+      <c r="I22" s="186" t="s">
         <v>372</v>
       </c>
-      <c r="J22" s="95"/>
+      <c r="J22" s="105"/>
     </row>
     <row r="23" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="97"/>
-      <c r="B23" s="97"/>
-      <c r="C23" s="109" t="s">
+      <c r="A23" s="101"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="130" t="s">
         <v>375</v>
       </c>
-      <c r="D23" s="94"/>
-      <c r="E23" s="97"/>
-      <c r="F23" s="97"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
       <c r="G23" s="52" t="s">
         <v>376</v>
       </c>
-      <c r="H23" s="97"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="105"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="107"/>
     </row>
     <row r="24" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="96" t="s">
+      <c r="A24" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B24" s="96" t="s">
+      <c r="B24" s="116" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="107" t="s">
+      <c r="C24" s="187" t="s">
         <v>379</v>
       </c>
-      <c r="D24" s="115" t="s">
+      <c r="D24" s="150" t="s">
         <v>380</v>
       </c>
       <c r="E24" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F24" s="112" t="s">
+      <c r="F24" s="182" t="s">
         <v>383</v>
       </c>
-      <c r="G24" s="94"/>
+      <c r="G24" s="110"/>
       <c r="H24" s="100" t="s">
         <v>175</v>
       </c>
       <c r="I24" s="50" t="s">
         <v>366</v>
       </c>
-      <c r="J24" s="115" t="s">
+      <c r="J24" s="150" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="97"/>
-      <c r="B25" s="97"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="111" t="s">
+      <c r="A25" s="101"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="143" t="s">
         <v>390</v>
       </c>
-      <c r="G25" s="94"/>
-      <c r="H25" s="97"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="101"/>
       <c r="I25" s="49" t="s">
         <v>214</v>
       </c>
-      <c r="J25" s="97"/>
+      <c r="J25" s="101"/>
     </row>
     <row r="26" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="96" t="s">
+      <c r="A26" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="B26" s="96" t="s">
+      <c r="B26" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="116" t="s">
+      <c r="C26" s="129" t="s">
         <v>392</v>
       </c>
-      <c r="D26" s="117" t="s">
+      <c r="D26" s="122" t="s">
         <v>394</v>
       </c>
       <c r="E26" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F26" s="122" t="s">
+      <c r="F26" s="140" t="s">
         <v>397</v>
       </c>
-      <c r="G26" s="119" t="s">
+      <c r="G26" s="118" t="s">
         <v>398</v>
       </c>
       <c r="H26" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I26" s="111" t="s">
+      <c r="I26" s="143" t="s">
         <v>399</v>
       </c>
-      <c r="J26" s="94"/>
+      <c r="J26" s="110"/>
     </row>
     <row r="27" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="97"/>
-      <c r="B27" s="97"/>
-      <c r="C27" s="97"/>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="97"/>
-      <c r="G27" s="97"/>
-      <c r="H27" s="97"/>
-      <c r="I27" s="112" t="s">
+      <c r="A27" s="101"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="101"/>
+      <c r="H27" s="101"/>
+      <c r="I27" s="182" t="s">
         <v>400</v>
       </c>
-      <c r="J27" s="94"/>
+      <c r="J27" s="110"/>
     </row>
     <row r="28" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="96" t="s">
+      <c r="A28" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="96" t="s">
+      <c r="B28" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="C28" s="120" t="s">
+      <c r="C28" s="159" t="s">
         <v>403</v>
       </c>
-      <c r="D28" s="123" t="s">
+      <c r="D28" s="121" t="s">
         <v>406</v>
       </c>
       <c r="E28" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F28" s="112" t="s">
+      <c r="F28" s="182" t="s">
         <v>410</v>
       </c>
-      <c r="G28" s="94"/>
+      <c r="G28" s="110"/>
       <c r="H28" s="100" t="s">
         <v>175</v>
       </c>
@@ -50187,16 +50402,16 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="97"/>
-      <c r="B29" s="97"/>
-      <c r="C29" s="97"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="97"/>
-      <c r="F29" s="111" t="s">
+      <c r="A29" s="101"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="101"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="143" t="s">
         <v>415</v>
       </c>
-      <c r="G29" s="94"/>
-      <c r="H29" s="97"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="101"/>
       <c r="I29" s="51" t="s">
         <v>352</v>
       </c>
@@ -50229,28 +50444,28 @@
       <c r="H30" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="I30" s="121" t="s">
+      <c r="I30" s="183" t="s">
         <v>424</v>
       </c>
-      <c r="J30" s="94"/>
+      <c r="J30" s="110"/>
     </row>
     <row r="31" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B31" s="96" t="s">
+      <c r="B31" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="119" t="s">
+      <c r="C31" s="118" t="s">
         <v>430</v>
       </c>
-      <c r="D31" s="120" t="s">
+      <c r="D31" s="159" t="s">
         <v>431</v>
       </c>
       <c r="E31" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F31" s="116" t="s">
+      <c r="F31" s="129" t="s">
         <v>433</v>
       </c>
       <c r="G31" s="51" t="s">
@@ -50259,38 +50474,38 @@
       <c r="H31" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I31" s="118" t="s">
+      <c r="I31" s="184" t="s">
         <v>436</v>
       </c>
-      <c r="J31" s="94"/>
+      <c r="J31" s="110"/>
     </row>
     <row r="32" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="97"/>
-      <c r="B32" s="97"/>
-      <c r="C32" s="97"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="97"/>
+      <c r="A32" s="101"/>
+      <c r="B32" s="101"/>
+      <c r="C32" s="101"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="101"/>
+      <c r="F32" s="101"/>
       <c r="G32" s="52" t="s">
         <v>438</v>
       </c>
-      <c r="H32" s="97"/>
-      <c r="I32" s="109" t="s">
+      <c r="H32" s="101"/>
+      <c r="I32" s="130" t="s">
         <v>439</v>
       </c>
-      <c r="J32" s="94"/>
+      <c r="J32" s="110"/>
     </row>
     <row r="33" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="96" t="s">
+      <c r="A33" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B33" s="96" t="s">
+      <c r="B33" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="117" t="s">
+      <c r="C33" s="122" t="s">
         <v>441</v>
       </c>
-      <c r="D33" s="119" t="s">
+      <c r="D33" s="118" t="s">
         <v>442</v>
       </c>
       <c r="E33" s="100" t="s">
@@ -50299,140 +50514,140 @@
       <c r="F33" s="50" t="s">
         <v>366</v>
       </c>
-      <c r="G33" s="96"/>
+      <c r="G33" s="116"/>
       <c r="H33" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I33" s="109" t="s">
+      <c r="I33" s="130" t="s">
         <v>445</v>
       </c>
-      <c r="J33" s="94"/>
+      <c r="J33" s="110"/>
     </row>
     <row r="34" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="97"/>
-      <c r="B34" s="97"/>
-      <c r="C34" s="97"/>
-      <c r="D34" s="97"/>
-      <c r="E34" s="97"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="101"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="101"/>
       <c r="F34" s="49" t="s">
         <v>214</v>
       </c>
-      <c r="G34" s="97"/>
-      <c r="H34" s="97"/>
-      <c r="I34" s="118" t="s">
+      <c r="G34" s="101"/>
+      <c r="H34" s="101"/>
+      <c r="I34" s="184" t="s">
         <v>448</v>
       </c>
-      <c r="J34" s="94"/>
+      <c r="J34" s="110"/>
     </row>
     <row r="35" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="96" t="s">
+      <c r="A35" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="96" t="s">
+      <c r="B35" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="C35" s="116" t="s">
+      <c r="C35" s="129" t="s">
         <v>451</v>
       </c>
-      <c r="D35" s="117" t="s">
+      <c r="D35" s="122" t="s">
         <v>454</v>
       </c>
-      <c r="E35" s="124" t="s">
+      <c r="E35" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F35" s="122" t="s">
+      <c r="F35" s="140" t="s">
         <v>457</v>
       </c>
-      <c r="G35" s="119" t="s">
+      <c r="G35" s="118" t="s">
         <v>459</v>
       </c>
-      <c r="H35" s="124" t="s">
+      <c r="H35" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I35" s="125" t="s">
+      <c r="I35" s="109" t="s">
         <v>461</v>
       </c>
-      <c r="J35" s="94"/>
+      <c r="J35" s="110"/>
     </row>
     <row r="36" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="97"/>
-      <c r="B36" s="97"/>
-      <c r="C36" s="97"/>
-      <c r="D36" s="97"/>
-      <c r="E36" s="97"/>
-      <c r="F36" s="97"/>
-      <c r="G36" s="97"/>
-      <c r="H36" s="97"/>
-      <c r="I36" s="126" t="s">
+      <c r="A36" s="101"/>
+      <c r="B36" s="101"/>
+      <c r="C36" s="101"/>
+      <c r="D36" s="101"/>
+      <c r="E36" s="101"/>
+      <c r="F36" s="101"/>
+      <c r="G36" s="101"/>
+      <c r="H36" s="101"/>
+      <c r="I36" s="181" t="s">
         <v>465</v>
       </c>
-      <c r="J36" s="94"/>
+      <c r="J36" s="110"/>
     </row>
     <row r="37" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="96" t="s">
+      <c r="A37" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="B37" s="96" t="s">
+      <c r="B37" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="C37" s="120" t="s">
+      <c r="C37" s="159" t="s">
         <v>471</v>
       </c>
-      <c r="D37" s="116" t="s">
+      <c r="D37" s="129" t="s">
         <v>473</v>
       </c>
-      <c r="E37" s="124" t="s">
+      <c r="E37" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F37" s="123" t="s">
+      <c r="F37" s="121" t="s">
         <v>476</v>
       </c>
-      <c r="G37" s="117" t="s">
+      <c r="G37" s="122" t="s">
         <v>477</v>
       </c>
-      <c r="H37" s="124" t="s">
+      <c r="H37" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I37" s="126" t="s">
+      <c r="I37" s="181" t="s">
         <v>480</v>
       </c>
-      <c r="J37" s="94"/>
+      <c r="J37" s="110"/>
     </row>
     <row r="38" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="97"/>
-      <c r="B38" s="97"/>
-      <c r="C38" s="97"/>
-      <c r="D38" s="97"/>
-      <c r="E38" s="97"/>
-      <c r="F38" s="97"/>
-      <c r="G38" s="97"/>
-      <c r="H38" s="97"/>
-      <c r="I38" s="125" t="s">
+      <c r="A38" s="101"/>
+      <c r="B38" s="101"/>
+      <c r="C38" s="101"/>
+      <c r="D38" s="101"/>
+      <c r="E38" s="101"/>
+      <c r="F38" s="101"/>
+      <c r="G38" s="101"/>
+      <c r="H38" s="101"/>
+      <c r="I38" s="109" t="s">
         <v>482</v>
       </c>
-      <c r="J38" s="94"/>
+      <c r="J38" s="110"/>
     </row>
     <row r="39" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="96" t="s">
+      <c r="A39" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="B39" s="96" t="s">
+      <c r="B39" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="C39" s="119" t="s">
+      <c r="C39" s="118" t="s">
         <v>485</v>
       </c>
-      <c r="D39" s="123" t="s">
+      <c r="D39" s="121" t="s">
         <v>486</v>
       </c>
-      <c r="E39" s="124" t="s">
+      <c r="E39" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="127" t="s">
+      <c r="F39" s="139" t="s">
         <v>488</v>
       </c>
-      <c r="G39" s="94"/>
-      <c r="H39" s="124" t="s">
+      <c r="G39" s="110"/>
+      <c r="H39" s="120" t="s">
         <v>175</v>
       </c>
       <c r="I39" s="63" t="s">
@@ -50443,16 +50658,16 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="97"/>
-      <c r="B40" s="97"/>
-      <c r="C40" s="97"/>
-      <c r="D40" s="97"/>
-      <c r="E40" s="97"/>
-      <c r="F40" s="128" t="s">
+      <c r="A40" s="101"/>
+      <c r="B40" s="101"/>
+      <c r="C40" s="101"/>
+      <c r="D40" s="101"/>
+      <c r="E40" s="101"/>
+      <c r="F40" s="158" t="s">
         <v>497</v>
       </c>
-      <c r="G40" s="94"/>
-      <c r="H40" s="97"/>
+      <c r="G40" s="110"/>
+      <c r="H40" s="101"/>
       <c r="I40" s="65" t="s">
         <v>352</v>
       </c>
@@ -50461,24 +50676,24 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="96" t="s">
+      <c r="A41" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="96" t="s">
+      <c r="B41" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="C41" s="128" t="s">
+      <c r="C41" s="158" t="s">
         <v>503</v>
       </c>
-      <c r="D41" s="94"/>
-      <c r="E41" s="124" t="s">
+      <c r="D41" s="110"/>
+      <c r="E41" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F41" s="122" t="s">
+      <c r="F41" s="140" t="s">
         <v>508</v>
       </c>
-      <c r="G41" s="123"/>
-      <c r="H41" s="124" t="s">
+      <c r="G41" s="121"/>
+      <c r="H41" s="120" t="s">
         <v>175</v>
       </c>
       <c r="I41" s="65" t="s">
@@ -50489,16 +50704,16 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="97"/>
-      <c r="B42" s="97"/>
-      <c r="C42" s="127" t="s">
+      <c r="A42" s="101"/>
+      <c r="B42" s="101"/>
+      <c r="C42" s="139" t="s">
         <v>509</v>
       </c>
-      <c r="D42" s="94"/>
-      <c r="E42" s="97"/>
-      <c r="F42" s="97"/>
-      <c r="G42" s="97"/>
-      <c r="H42" s="97"/>
+      <c r="D42" s="110"/>
+      <c r="E42" s="101"/>
+      <c r="F42" s="101"/>
+      <c r="G42" s="101"/>
+      <c r="H42" s="101"/>
       <c r="I42" s="63" t="s">
         <v>510</v>
       </c>
@@ -50507,291 +50722,291 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="96" t="s">
+      <c r="A43" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B43" s="96" t="s">
+      <c r="B43" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="C43" s="142" t="s">
+      <c r="C43" s="167" t="s">
         <v>512</v>
       </c>
-      <c r="D43" s="143" t="s">
+      <c r="D43" s="168" t="s">
         <v>515</v>
       </c>
-      <c r="E43" s="124" t="s">
+      <c r="E43" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="G43" s="129" t="s">
+      <c r="G43" s="180" t="s">
         <v>517</v>
       </c>
-      <c r="H43" s="124" t="s">
+      <c r="H43" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I43" s="130" t="s">
+      <c r="I43" s="160" t="s">
         <v>520</v>
       </c>
-      <c r="J43" s="95"/>
+      <c r="J43" s="105"/>
     </row>
     <row r="44" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="97"/>
-      <c r="B44" s="97"/>
-      <c r="C44" s="97"/>
-      <c r="D44" s="97"/>
-      <c r="E44" s="97"/>
-      <c r="G44" s="97"/>
-      <c r="H44" s="97"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="105"/>
+      <c r="A44" s="101"/>
+      <c r="B44" s="101"/>
+      <c r="C44" s="101"/>
+      <c r="D44" s="101"/>
+      <c r="E44" s="101"/>
+      <c r="G44" s="101"/>
+      <c r="H44" s="101"/>
+      <c r="I44" s="106"/>
+      <c r="J44" s="107"/>
     </row>
     <row r="45" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="96" t="s">
+      <c r="A45" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="B45" s="96" t="s">
+      <c r="B45" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="C45" s="116" t="s">
+      <c r="C45" s="129" t="s">
         <v>527</v>
       </c>
-      <c r="D45" s="117" t="s">
+      <c r="D45" s="122" t="s">
         <v>528</v>
       </c>
-      <c r="E45" s="124" t="s">
+      <c r="E45" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F45" s="131" t="s">
+      <c r="F45" s="161" t="s">
         <v>531</v>
       </c>
-      <c r="G45" s="94"/>
-      <c r="H45" s="124" t="s">
+      <c r="G45" s="110"/>
+      <c r="H45" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I45" s="130" t="s">
+      <c r="I45" s="160" t="s">
         <v>534</v>
       </c>
-      <c r="J45" s="95"/>
+      <c r="J45" s="105"/>
     </row>
     <row r="46" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="97"/>
-      <c r="B46" s="97"/>
-      <c r="C46" s="97"/>
-      <c r="D46" s="97"/>
-      <c r="E46" s="97"/>
-      <c r="F46" s="125" t="s">
+      <c r="A46" s="101"/>
+      <c r="B46" s="101"/>
+      <c r="C46" s="101"/>
+      <c r="D46" s="101"/>
+      <c r="E46" s="101"/>
+      <c r="F46" s="109" t="s">
         <v>536</v>
       </c>
-      <c r="G46" s="94"/>
-      <c r="H46" s="97"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="105"/>
+      <c r="G46" s="110"/>
+      <c r="H46" s="101"/>
+      <c r="I46" s="106"/>
+      <c r="J46" s="107"/>
     </row>
     <row r="47" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="96" t="s">
+      <c r="A47" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="B47" s="96" t="s">
+      <c r="B47" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="C47" s="116" t="s">
+      <c r="C47" s="129" t="s">
         <v>543</v>
       </c>
-      <c r="D47" s="120" t="s">
+      <c r="D47" s="159" t="s">
         <v>544</v>
       </c>
-      <c r="E47" s="124" t="s">
+      <c r="E47" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F47" s="116"/>
+      <c r="F47" s="129"/>
       <c r="G47" s="69" t="s">
         <v>352</v>
       </c>
-      <c r="H47" s="124" t="s">
+      <c r="H47" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I47" s="125" t="s">
+      <c r="I47" s="109" t="s">
         <v>548</v>
       </c>
-      <c r="J47" s="94"/>
+      <c r="J47" s="110"/>
     </row>
     <row r="48" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="97"/>
-      <c r="B48" s="97"/>
-      <c r="C48" s="97"/>
-      <c r="D48" s="97"/>
-      <c r="E48" s="97"/>
-      <c r="F48" s="97"/>
+      <c r="A48" s="101"/>
+      <c r="B48" s="101"/>
+      <c r="C48" s="101"/>
+      <c r="D48" s="101"/>
+      <c r="E48" s="101"/>
+      <c r="F48" s="101"/>
       <c r="G48" s="58" t="s">
         <v>551</v>
       </c>
-      <c r="H48" s="97"/>
-      <c r="I48" s="131" t="s">
+      <c r="H48" s="101"/>
+      <c r="I48" s="161" t="s">
         <v>552</v>
       </c>
-      <c r="J48" s="94"/>
+      <c r="J48" s="110"/>
     </row>
     <row r="49" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="96" t="s">
+      <c r="A49" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="B49" s="96" t="s">
+      <c r="B49" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="C49" s="145" t="s">
+      <c r="C49" s="165" t="s">
         <v>554</v>
       </c>
-      <c r="D49" s="146" t="s">
+      <c r="D49" s="166" t="s">
         <v>556</v>
       </c>
-      <c r="E49" s="124" t="s">
+      <c r="E49" s="120" t="s">
         <v>169</v>
       </c>
       <c r="F49" s="58" t="s">
         <v>558</v>
       </c>
-      <c r="G49" s="132" t="s">
+      <c r="G49" s="177" t="s">
         <v>560</v>
       </c>
-      <c r="H49" s="124" t="s">
+      <c r="H49" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I49" s="133" t="s">
+      <c r="I49" s="178" t="s">
         <v>565</v>
       </c>
-      <c r="J49" s="134" t="s">
+      <c r="J49" s="179" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="97"/>
-      <c r="B50" s="97"/>
-      <c r="C50" s="97"/>
-      <c r="D50" s="97"/>
-      <c r="E50" s="97"/>
+      <c r="A50" s="101"/>
+      <c r="B50" s="101"/>
+      <c r="C50" s="101"/>
+      <c r="D50" s="101"/>
+      <c r="E50" s="101"/>
       <c r="F50" s="69" t="s">
         <v>352</v>
       </c>
-      <c r="G50" s="97"/>
-      <c r="H50" s="97"/>
-      <c r="I50" s="97"/>
-      <c r="J50" s="97"/>
+      <c r="G50" s="101"/>
+      <c r="H50" s="101"/>
+      <c r="I50" s="101"/>
+      <c r="J50" s="101"/>
     </row>
     <row r="51" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="96" t="s">
+      <c r="A51" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B51" s="96" t="s">
+      <c r="B51" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="C51" s="120" t="s">
+      <c r="C51" s="159" t="s">
         <v>572</v>
       </c>
-      <c r="D51" s="116" t="s">
+      <c r="D51" s="129" t="s">
         <v>574</v>
       </c>
-      <c r="E51" s="124" t="s">
+      <c r="E51" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F51" s="144" t="s">
+      <c r="F51" s="119" t="s">
         <v>578</v>
       </c>
       <c r="G51" s="64" t="s">
         <v>366</v>
       </c>
-      <c r="H51" s="124" t="s">
+      <c r="H51" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I51" s="128" t="s">
+      <c r="I51" s="158" t="s">
         <v>581</v>
       </c>
-      <c r="J51" s="94"/>
+      <c r="J51" s="110"/>
     </row>
     <row r="52" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="97"/>
-      <c r="B52" s="97"/>
-      <c r="C52" s="97"/>
-      <c r="D52" s="97"/>
-      <c r="E52" s="97"/>
-      <c r="F52" s="97"/>
+      <c r="A52" s="101"/>
+      <c r="B52" s="101"/>
+      <c r="C52" s="101"/>
+      <c r="D52" s="101"/>
+      <c r="E52" s="101"/>
+      <c r="F52" s="101"/>
       <c r="G52" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="H52" s="97"/>
-      <c r="I52" s="127" t="s">
+      <c r="H52" s="101"/>
+      <c r="I52" s="139" t="s">
         <v>584</v>
       </c>
-      <c r="J52" s="94"/>
+      <c r="J52" s="110"/>
     </row>
     <row r="53" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="96" t="s">
+      <c r="A53" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B53" s="96" t="s">
+      <c r="B53" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="C53" s="144" t="s">
+      <c r="C53" s="119" t="s">
         <v>587</v>
       </c>
-      <c r="D53" s="123" t="s">
+      <c r="D53" s="121" t="s">
         <v>588</v>
       </c>
-      <c r="E53" s="124" t="s">
+      <c r="E53" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F53" s="116" t="s">
+      <c r="F53" s="129" t="s">
         <v>589</v>
       </c>
       <c r="G53" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="H53" s="124" t="s">
+      <c r="H53" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I53" s="127" t="s">
+      <c r="I53" s="139" t="s">
         <v>590</v>
       </c>
-      <c r="J53" s="94"/>
+      <c r="J53" s="110"/>
     </row>
     <row r="54" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="97"/>
-      <c r="B54" s="97"/>
-      <c r="C54" s="97"/>
-      <c r="D54" s="97"/>
-      <c r="E54" s="97"/>
-      <c r="F54" s="97"/>
+      <c r="A54" s="101"/>
+      <c r="B54" s="101"/>
+      <c r="C54" s="101"/>
+      <c r="D54" s="101"/>
+      <c r="E54" s="101"/>
+      <c r="F54" s="101"/>
       <c r="G54" s="64" t="s">
         <v>366</v>
       </c>
-      <c r="H54" s="97"/>
-      <c r="I54" s="128" t="s">
+      <c r="H54" s="101"/>
+      <c r="I54" s="158" t="s">
         <v>592</v>
       </c>
-      <c r="J54" s="94"/>
+      <c r="J54" s="110"/>
     </row>
     <row r="55" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="96" t="s">
+      <c r="A55" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="B55" s="96" t="s">
+      <c r="B55" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="C55" s="131" t="s">
+      <c r="C55" s="161" t="s">
         <v>596</v>
       </c>
-      <c r="D55" s="94"/>
-      <c r="E55" s="124" t="s">
+      <c r="D55" s="110"/>
+      <c r="E55" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F55" s="122" t="s">
+      <c r="F55" s="140" t="s">
         <v>598</v>
       </c>
-      <c r="G55" s="119" t="s">
+      <c r="G55" s="118" t="s">
         <v>600</v>
       </c>
-      <c r="H55" s="124" t="s">
+      <c r="H55" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I55" s="155" t="s">
+      <c r="I55" s="162" t="s">
         <v>601</v>
       </c>
       <c r="J55" s="65" t="s">
@@ -50799,131 +51014,131 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="97"/>
-      <c r="B56" s="97"/>
-      <c r="C56" s="125" t="s">
+      <c r="A56" s="101"/>
+      <c r="B56" s="101"/>
+      <c r="C56" s="109" t="s">
         <v>604</v>
       </c>
-      <c r="D56" s="94"/>
-      <c r="E56" s="97"/>
-      <c r="F56" s="97"/>
-      <c r="G56" s="97"/>
-      <c r="H56" s="97"/>
-      <c r="I56" s="97"/>
+      <c r="D56" s="110"/>
+      <c r="E56" s="101"/>
+      <c r="F56" s="101"/>
+      <c r="G56" s="101"/>
+      <c r="H56" s="101"/>
+      <c r="I56" s="101"/>
       <c r="J56" s="56" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="96" t="s">
+      <c r="A57" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="96" t="s">
+      <c r="B57" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="C57" s="125" t="s">
+      <c r="C57" s="109" t="s">
         <v>611</v>
       </c>
-      <c r="D57" s="94"/>
-      <c r="E57" s="124" t="s">
+      <c r="D57" s="110"/>
+      <c r="E57" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F57" s="120" t="s">
+      <c r="F57" s="159" t="s">
         <v>616</v>
       </c>
-      <c r="G57" s="123" t="s">
+      <c r="G57" s="121" t="s">
         <v>617</v>
       </c>
-      <c r="H57" s="124" t="s">
+      <c r="H57" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I57" s="130" t="s">
+      <c r="I57" s="160" t="s">
         <v>618</v>
       </c>
-      <c r="J57" s="95"/>
+      <c r="J57" s="105"/>
     </row>
     <row r="58" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="97"/>
-      <c r="B58" s="97"/>
-      <c r="C58" s="131" t="s">
+      <c r="A58" s="101"/>
+      <c r="B58" s="101"/>
+      <c r="C58" s="161" t="s">
         <v>619</v>
       </c>
-      <c r="D58" s="94"/>
-      <c r="E58" s="97"/>
-      <c r="F58" s="97"/>
-      <c r="G58" s="97"/>
-      <c r="H58" s="97"/>
-      <c r="I58" s="104"/>
-      <c r="J58" s="105"/>
+      <c r="D58" s="110"/>
+      <c r="E58" s="101"/>
+      <c r="F58" s="101"/>
+      <c r="G58" s="101"/>
+      <c r="H58" s="101"/>
+      <c r="I58" s="106"/>
+      <c r="J58" s="107"/>
     </row>
     <row r="59" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="96" t="s">
+      <c r="A59" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="96" t="s">
+      <c r="B59" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="C59" s="119" t="s">
+      <c r="C59" s="118" t="s">
         <v>623</v>
       </c>
-      <c r="D59" s="120" t="s">
+      <c r="D59" s="159" t="s">
         <v>624</v>
       </c>
-      <c r="E59" s="124" t="s">
+      <c r="E59" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F59" s="116" t="s">
+      <c r="F59" s="129" t="s">
         <v>627</v>
       </c>
-      <c r="G59" s="122" t="s">
+      <c r="G59" s="140" t="s">
         <v>628</v>
       </c>
-      <c r="H59" s="124" t="s">
+      <c r="H59" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I59" s="128" t="s">
+      <c r="I59" s="158" t="s">
         <v>629</v>
       </c>
-      <c r="J59" s="94"/>
+      <c r="J59" s="110"/>
     </row>
     <row r="60" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="97"/>
-      <c r="B60" s="97"/>
-      <c r="C60" s="97"/>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="127" t="s">
+      <c r="A60" s="101"/>
+      <c r="B60" s="101"/>
+      <c r="C60" s="101"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="139" t="s">
         <v>630</v>
       </c>
-      <c r="J60" s="94"/>
+      <c r="J60" s="110"/>
     </row>
     <row r="61" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="96" t="s">
+      <c r="A61" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B61" s="96" t="s">
+      <c r="B61" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="C61" s="116" t="s">
+      <c r="C61" s="129" t="s">
         <v>635</v>
       </c>
-      <c r="D61" s="123" t="s">
+      <c r="D61" s="121" t="s">
         <v>636</v>
       </c>
-      <c r="E61" s="124" t="s">
+      <c r="E61" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F61" s="127" t="s">
+      <c r="F61" s="139" t="s">
         <v>639</v>
       </c>
-      <c r="G61" s="94"/>
-      <c r="H61" s="124" t="s">
+      <c r="G61" s="110"/>
+      <c r="H61" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I61" s="120" t="s">
+      <c r="I61" s="159" t="s">
         <v>642</v>
       </c>
       <c r="J61" s="66" t="s">
@@ -50931,42 +51146,42 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="97"/>
-      <c r="B62" s="97"/>
-      <c r="C62" s="97"/>
-      <c r="D62" s="97"/>
-      <c r="E62" s="97"/>
-      <c r="F62" s="128" t="s">
+      <c r="A62" s="101"/>
+      <c r="B62" s="101"/>
+      <c r="C62" s="101"/>
+      <c r="D62" s="101"/>
+      <c r="E62" s="101"/>
+      <c r="F62" s="158" t="s">
         <v>645</v>
       </c>
-      <c r="G62" s="94"/>
-      <c r="H62" s="97"/>
-      <c r="I62" s="97"/>
+      <c r="G62" s="110"/>
+      <c r="H62" s="101"/>
+      <c r="I62" s="101"/>
       <c r="J62" s="64" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="96" t="s">
+      <c r="A63" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B63" s="96" t="s">
+      <c r="B63" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="C63" s="116" t="s">
+      <c r="C63" s="129" t="s">
         <v>646</v>
       </c>
-      <c r="D63" s="119" t="s">
+      <c r="D63" s="118" t="s">
         <v>648</v>
       </c>
-      <c r="E63" s="124" t="s">
+      <c r="E63" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F63" s="122" t="s">
+      <c r="F63" s="140" t="s">
         <v>650</v>
       </c>
-      <c r="G63" s="169"/>
-      <c r="H63" s="124" t="s">
+      <c r="G63" s="146"/>
+      <c r="H63" s="120" t="s">
         <v>175</v>
       </c>
       <c r="I63" s="56" t="s">
@@ -50977,14 +51192,14 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="97"/>
-      <c r="B64" s="97"/>
-      <c r="C64" s="97"/>
-      <c r="D64" s="97"/>
-      <c r="E64" s="97"/>
-      <c r="F64" s="97"/>
-      <c r="G64" s="97"/>
-      <c r="H64" s="97"/>
+      <c r="A64" s="101"/>
+      <c r="B64" s="101"/>
+      <c r="C64" s="101"/>
+      <c r="D64" s="101"/>
+      <c r="E64" s="101"/>
+      <c r="F64" s="101"/>
+      <c r="G64" s="101"/>
+      <c r="H64" s="101"/>
       <c r="I64" s="65" t="s">
         <v>352</v>
       </c>
@@ -50993,89 +51208,89 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="96" t="s">
+      <c r="A65" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="B65" s="96" t="s">
+      <c r="B65" s="116" t="s">
         <v>159</v>
       </c>
-      <c r="C65" s="173" t="s">
+      <c r="C65" s="144" t="s">
         <v>652</v>
       </c>
-      <c r="D65" s="170" t="s">
+      <c r="D65" s="145" t="s">
         <v>653</v>
       </c>
       <c r="E65" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F65" s="149" t="s">
+      <c r="F65" s="141" t="s">
         <v>654</v>
       </c>
-      <c r="G65" s="94"/>
+      <c r="G65" s="110"/>
       <c r="H65" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I65" s="109" t="s">
+      <c r="I65" s="130" t="s">
         <v>655</v>
       </c>
-      <c r="J65" s="94"/>
+      <c r="J65" s="110"/>
     </row>
     <row r="66" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="147"/>
-      <c r="B66" s="147"/>
-      <c r="C66" s="147"/>
-      <c r="D66" s="147"/>
-      <c r="E66" s="147"/>
-      <c r="F66" s="162" t="s">
+      <c r="A66" s="117"/>
+      <c r="B66" s="117"/>
+      <c r="C66" s="117"/>
+      <c r="D66" s="117"/>
+      <c r="E66" s="117"/>
+      <c r="F66" s="142" t="s">
         <v>656</v>
       </c>
-      <c r="G66" s="94"/>
-      <c r="H66" s="147"/>
-      <c r="I66" s="156" t="s">
+      <c r="G66" s="110"/>
+      <c r="H66" s="117"/>
+      <c r="I66" s="126" t="s">
         <v>657</v>
       </c>
-      <c r="J66" s="157" t="s">
+      <c r="J66" s="127" t="s">
         <v>658</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="97"/>
-      <c r="B67" s="97"/>
-      <c r="C67" s="97"/>
-      <c r="D67" s="97"/>
-      <c r="E67" s="97"/>
-      <c r="F67" s="138" t="s">
+      <c r="A67" s="101"/>
+      <c r="B67" s="101"/>
+      <c r="C67" s="101"/>
+      <c r="D67" s="101"/>
+      <c r="E67" s="101"/>
+      <c r="F67" s="114" t="s">
         <v>659</v>
       </c>
-      <c r="G67" s="94"/>
-      <c r="H67" s="97"/>
-      <c r="I67" s="97"/>
-      <c r="J67" s="97"/>
+      <c r="G67" s="110"/>
+      <c r="H67" s="101"/>
+      <c r="I67" s="101"/>
+      <c r="J67" s="101"/>
     </row>
     <row r="68" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="96" t="s">
+      <c r="A68" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="B68" s="96" t="s">
+      <c r="B68" s="116" t="s">
         <v>159</v>
       </c>
-      <c r="C68" s="174" t="s">
+      <c r="C68" s="111" t="s">
         <v>660</v>
       </c>
-      <c r="D68" s="170" t="s">
+      <c r="D68" s="145" t="s">
         <v>661</v>
       </c>
       <c r="E68" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F68" s="149" t="s">
+      <c r="F68" s="141" t="s">
         <v>662</v>
       </c>
-      <c r="G68" s="94"/>
+      <c r="G68" s="110"/>
       <c r="H68" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I68" s="171" t="s">
+      <c r="I68" s="128" t="s">
         <v>663</v>
       </c>
       <c r="J68" s="33" t="s">
@@ -51083,57 +51298,57 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="147"/>
-      <c r="B69" s="147"/>
-      <c r="C69" s="147"/>
-      <c r="D69" s="147"/>
-      <c r="E69" s="147"/>
-      <c r="F69" s="162" t="s">
+      <c r="A69" s="117"/>
+      <c r="B69" s="117"/>
+      <c r="C69" s="117"/>
+      <c r="D69" s="117"/>
+      <c r="E69" s="117"/>
+      <c r="F69" s="142" t="s">
         <v>664</v>
       </c>
-      <c r="G69" s="94"/>
-      <c r="H69" s="147"/>
-      <c r="I69" s="147"/>
-      <c r="J69" s="172" t="s">
+      <c r="G69" s="110"/>
+      <c r="H69" s="117"/>
+      <c r="I69" s="117"/>
+      <c r="J69" s="156" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="97"/>
-      <c r="B70" s="97"/>
-      <c r="C70" s="97"/>
-      <c r="D70" s="97"/>
-      <c r="E70" s="97"/>
-      <c r="F70" s="111" t="s">
+      <c r="A70" s="101"/>
+      <c r="B70" s="101"/>
+      <c r="C70" s="101"/>
+      <c r="D70" s="101"/>
+      <c r="E70" s="101"/>
+      <c r="F70" s="143" t="s">
         <v>665</v>
       </c>
-      <c r="G70" s="94"/>
-      <c r="H70" s="97"/>
-      <c r="I70" s="97"/>
-      <c r="J70" s="97"/>
+      <c r="G70" s="110"/>
+      <c r="H70" s="101"/>
+      <c r="I70" s="101"/>
+      <c r="J70" s="101"/>
     </row>
     <row r="71" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="96" t="s">
+      <c r="A71" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="B71" s="96" t="s">
+      <c r="B71" s="116" t="s">
         <v>159</v>
       </c>
-      <c r="C71" s="109" t="s">
+      <c r="C71" s="130" t="s">
         <v>666</v>
       </c>
-      <c r="D71" s="94"/>
+      <c r="D71" s="110"/>
       <c r="E71" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F71" s="138" t="s">
+      <c r="F71" s="114" t="s">
         <v>667</v>
       </c>
-      <c r="G71" s="94"/>
+      <c r="G71" s="110"/>
       <c r="H71" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I71" s="173" t="s">
+      <c r="I71" s="144" t="s">
         <v>668</v>
       </c>
       <c r="J71" s="36" t="s">
@@ -51141,93 +51356,93 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="147"/>
-      <c r="B72" s="147"/>
-      <c r="C72" s="156" t="s">
+      <c r="A72" s="117"/>
+      <c r="B72" s="117"/>
+      <c r="C72" s="126" t="s">
         <v>669</v>
       </c>
-      <c r="D72" s="157" t="s">
+      <c r="D72" s="127" t="s">
         <v>670</v>
       </c>
-      <c r="E72" s="147"/>
-      <c r="F72" s="149" t="s">
+      <c r="E72" s="117"/>
+      <c r="F72" s="141" t="s">
         <v>671</v>
       </c>
-      <c r="G72" s="94"/>
-      <c r="H72" s="147"/>
-      <c r="I72" s="147"/>
-      <c r="J72" s="175" t="s">
+      <c r="G72" s="110"/>
+      <c r="H72" s="117"/>
+      <c r="I72" s="117"/>
+      <c r="J72" s="157" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="97"/>
-      <c r="B73" s="97"/>
-      <c r="C73" s="97"/>
-      <c r="D73" s="97"/>
-      <c r="E73" s="97"/>
-      <c r="F73" s="162" t="s">
+      <c r="A73" s="101"/>
+      <c r="B73" s="101"/>
+      <c r="C73" s="101"/>
+      <c r="D73" s="101"/>
+      <c r="E73" s="101"/>
+      <c r="F73" s="142" t="s">
         <v>672</v>
       </c>
-      <c r="G73" s="94"/>
-      <c r="H73" s="97"/>
-      <c r="I73" s="97"/>
-      <c r="J73" s="97"/>
+      <c r="G73" s="110"/>
+      <c r="H73" s="101"/>
+      <c r="I73" s="101"/>
+      <c r="J73" s="101"/>
     </row>
     <row r="74" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="96" t="s">
+      <c r="A74" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B74" s="96" t="s">
+      <c r="B74" s="116" t="s">
         <v>159</v>
       </c>
-      <c r="C74" s="171" t="s">
+      <c r="C74" s="128" t="s">
         <v>673</v>
       </c>
-      <c r="D74" s="179" t="s">
+      <c r="D74" s="115" t="s">
         <v>674</v>
       </c>
       <c r="E74" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F74" s="149" t="s">
+      <c r="F74" s="141" t="s">
         <v>675</v>
       </c>
-      <c r="G74" s="94"/>
+      <c r="G74" s="110"/>
       <c r="H74" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I74" s="174" t="s">
+      <c r="I74" s="111" t="s">
         <v>676</v>
       </c>
       <c r="J74" s="28"/>
     </row>
     <row r="75" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="147"/>
-      <c r="B75" s="147"/>
-      <c r="C75" s="147"/>
-      <c r="D75" s="147"/>
-      <c r="E75" s="147"/>
-      <c r="F75" s="162" t="s">
+      <c r="A75" s="117"/>
+      <c r="B75" s="117"/>
+      <c r="C75" s="117"/>
+      <c r="D75" s="117"/>
+      <c r="E75" s="117"/>
+      <c r="F75" s="142" t="s">
         <v>677</v>
       </c>
-      <c r="G75" s="94"/>
-      <c r="H75" s="147"/>
-      <c r="I75" s="147"/>
+      <c r="G75" s="110"/>
+      <c r="H75" s="117"/>
+      <c r="I75" s="117"/>
       <c r="J75" s="73"/>
     </row>
     <row r="76" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="97"/>
-      <c r="B76" s="97"/>
-      <c r="C76" s="97"/>
-      <c r="D76" s="97"/>
-      <c r="E76" s="97"/>
-      <c r="F76" s="111" t="s">
+      <c r="A76" s="101"/>
+      <c r="B76" s="101"/>
+      <c r="C76" s="101"/>
+      <c r="D76" s="101"/>
+      <c r="E76" s="101"/>
+      <c r="F76" s="143" t="s">
         <v>678</v>
       </c>
-      <c r="G76" s="94"/>
-      <c r="H76" s="97"/>
-      <c r="I76" s="97"/>
+      <c r="G76" s="110"/>
+      <c r="H76" s="101"/>
+      <c r="I76" s="101"/>
       <c r="J76" s="74"/>
     </row>
     <row r="77" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -51263,218 +51478,218 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="96" t="s">
+      <c r="A78" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="B78" s="96" t="s">
+      <c r="B78" s="116" t="s">
         <v>172</v>
       </c>
-      <c r="C78" s="116" t="s">
+      <c r="C78" s="129" t="s">
         <v>685</v>
       </c>
-      <c r="D78" s="117" t="s">
+      <c r="D78" s="122" t="s">
         <v>686</v>
       </c>
-      <c r="E78" s="124" t="s">
+      <c r="E78" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F78" s="119" t="s">
+      <c r="F78" s="118" t="s">
         <v>687</v>
       </c>
-      <c r="G78" s="176" t="s">
+      <c r="G78" s="138" t="s">
         <v>214</v>
       </c>
-      <c r="H78" s="124" t="s">
+      <c r="H78" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I78" s="158" t="s">
+      <c r="I78" s="134" t="s">
         <v>688</v>
       </c>
-      <c r="J78" s="94"/>
+      <c r="J78" s="110"/>
     </row>
     <row r="79" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="147"/>
-      <c r="B79" s="147"/>
-      <c r="C79" s="147"/>
-      <c r="D79" s="147"/>
-      <c r="E79" s="147"/>
-      <c r="F79" s="147"/>
-      <c r="G79" s="97"/>
-      <c r="H79" s="147"/>
-      <c r="I79" s="159" t="s">
+      <c r="A79" s="117"/>
+      <c r="B79" s="117"/>
+      <c r="C79" s="117"/>
+      <c r="D79" s="117"/>
+      <c r="E79" s="117"/>
+      <c r="F79" s="117"/>
+      <c r="G79" s="101"/>
+      <c r="H79" s="117"/>
+      <c r="I79" s="135" t="s">
         <v>689</v>
       </c>
-      <c r="J79" s="94"/>
+      <c r="J79" s="110"/>
     </row>
     <row r="80" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="97"/>
-      <c r="B80" s="97"/>
-      <c r="C80" s="97"/>
-      <c r="D80" s="97"/>
-      <c r="E80" s="97"/>
-      <c r="F80" s="97"/>
+      <c r="A80" s="101"/>
+      <c r="B80" s="101"/>
+      <c r="C80" s="101"/>
+      <c r="D80" s="101"/>
+      <c r="E80" s="101"/>
+      <c r="F80" s="101"/>
       <c r="G80" s="79" t="s">
         <v>231</v>
       </c>
-      <c r="H80" s="97"/>
-      <c r="I80" s="127" t="s">
+      <c r="H80" s="101"/>
+      <c r="I80" s="139" t="s">
         <v>690</v>
       </c>
-      <c r="J80" s="94"/>
+      <c r="J80" s="110"/>
     </row>
     <row r="81" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="96" t="s">
+      <c r="A81" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="B81" s="96" t="s">
+      <c r="B81" s="116" t="s">
         <v>172</v>
       </c>
-      <c r="C81" s="123" t="s">
+      <c r="C81" s="121" t="s">
         <v>691</v>
       </c>
-      <c r="D81" s="144" t="s">
+      <c r="D81" s="119" t="s">
         <v>692</v>
       </c>
-      <c r="E81" s="124" t="s">
+      <c r="E81" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F81" s="116" t="s">
+      <c r="F81" s="129" t="s">
         <v>693</v>
       </c>
-      <c r="G81" s="117" t="s">
+      <c r="G81" s="122" t="s">
         <v>694</v>
       </c>
-      <c r="H81" s="124" t="s">
+      <c r="H81" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I81" s="158" t="s">
+      <c r="I81" s="134" t="s">
         <v>695</v>
       </c>
-      <c r="J81" s="94"/>
+      <c r="J81" s="110"/>
     </row>
     <row r="82" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="147"/>
-      <c r="B82" s="147"/>
-      <c r="C82" s="147"/>
-      <c r="D82" s="147"/>
-      <c r="E82" s="147"/>
-      <c r="F82" s="147"/>
-      <c r="G82" s="147"/>
-      <c r="H82" s="147"/>
-      <c r="I82" s="159" t="s">
+      <c r="A82" s="117"/>
+      <c r="B82" s="117"/>
+      <c r="C82" s="117"/>
+      <c r="D82" s="117"/>
+      <c r="E82" s="117"/>
+      <c r="F82" s="117"/>
+      <c r="G82" s="117"/>
+      <c r="H82" s="117"/>
+      <c r="I82" s="135" t="s">
         <v>696</v>
       </c>
-      <c r="J82" s="94"/>
+      <c r="J82" s="110"/>
     </row>
     <row r="83" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="97"/>
-      <c r="B83" s="97"/>
-      <c r="C83" s="97"/>
-      <c r="D83" s="97"/>
-      <c r="E83" s="97"/>
-      <c r="F83" s="97"/>
-      <c r="G83" s="97"/>
-      <c r="H83" s="97"/>
-      <c r="I83" s="151" t="s">
+      <c r="A83" s="101"/>
+      <c r="B83" s="101"/>
+      <c r="C83" s="101"/>
+      <c r="D83" s="101"/>
+      <c r="E83" s="101"/>
+      <c r="F83" s="101"/>
+      <c r="G83" s="101"/>
+      <c r="H83" s="101"/>
+      <c r="I83" s="136" t="s">
         <v>697</v>
       </c>
-      <c r="J83" s="94"/>
+      <c r="J83" s="110"/>
     </row>
     <row r="84" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="96" t="s">
+      <c r="A84" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="B84" s="96" t="s">
+      <c r="B84" s="116" t="s">
         <v>172</v>
       </c>
-      <c r="C84" s="119" t="s">
+      <c r="C84" s="118" t="s">
         <v>698</v>
       </c>
-      <c r="D84" s="144" t="s">
+      <c r="D84" s="119" t="s">
         <v>699</v>
       </c>
-      <c r="E84" s="124" t="s">
+      <c r="E84" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F84" s="123" t="s">
+      <c r="F84" s="121" t="s">
         <v>700</v>
       </c>
-      <c r="G84" s="122" t="s">
+      <c r="G84" s="140" t="s">
         <v>701</v>
       </c>
-      <c r="H84" s="124" t="s">
+      <c r="H84" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I84" s="158" t="s">
+      <c r="I84" s="134" t="s">
         <v>702</v>
       </c>
-      <c r="J84" s="94"/>
+      <c r="J84" s="110"/>
     </row>
     <row r="85" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="147"/>
-      <c r="B85" s="147"/>
-      <c r="C85" s="147"/>
-      <c r="D85" s="147"/>
-      <c r="E85" s="147"/>
-      <c r="F85" s="147"/>
-      <c r="G85" s="147"/>
-      <c r="H85" s="147"/>
-      <c r="I85" s="159" t="s">
+      <c r="A85" s="117"/>
+      <c r="B85" s="117"/>
+      <c r="C85" s="117"/>
+      <c r="D85" s="117"/>
+      <c r="E85" s="117"/>
+      <c r="F85" s="117"/>
+      <c r="G85" s="117"/>
+      <c r="H85" s="117"/>
+      <c r="I85" s="135" t="s">
         <v>703</v>
       </c>
-      <c r="J85" s="94"/>
+      <c r="J85" s="110"/>
     </row>
     <row r="86" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="97"/>
-      <c r="B86" s="97"/>
-      <c r="C86" s="97"/>
-      <c r="D86" s="97"/>
-      <c r="E86" s="97"/>
-      <c r="F86" s="97"/>
-      <c r="G86" s="97"/>
-      <c r="H86" s="97"/>
-      <c r="I86" s="127" t="s">
+      <c r="A86" s="101"/>
+      <c r="B86" s="101"/>
+      <c r="C86" s="101"/>
+      <c r="D86" s="101"/>
+      <c r="E86" s="101"/>
+      <c r="F86" s="101"/>
+      <c r="G86" s="101"/>
+      <c r="H86" s="101"/>
+      <c r="I86" s="139" t="s">
         <v>704</v>
       </c>
-      <c r="J86" s="94"/>
+      <c r="J86" s="110"/>
     </row>
     <row r="87" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="96" t="s">
+      <c r="A87" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B87" s="96" t="s">
+      <c r="B87" s="116" t="s">
         <v>172</v>
       </c>
-      <c r="C87" s="116" t="s">
+      <c r="C87" s="129" t="s">
         <v>705</v>
       </c>
-      <c r="D87" s="119" t="s">
+      <c r="D87" s="118" t="s">
         <v>706</v>
       </c>
-      <c r="E87" s="124" t="s">
+      <c r="E87" s="120" t="s">
         <v>169</v>
       </c>
       <c r="G87" s="79" t="s">
         <v>231</v>
       </c>
-      <c r="H87" s="124" t="s">
+      <c r="H87" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I87" s="125" t="s">
+      <c r="I87" s="109" t="s">
         <v>707</v>
       </c>
-      <c r="J87" s="94"/>
+      <c r="J87" s="110"/>
     </row>
     <row r="88" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="97"/>
-      <c r="B88" s="97"/>
-      <c r="C88" s="97"/>
-      <c r="D88" s="97"/>
-      <c r="E88" s="97"/>
+      <c r="A88" s="101"/>
+      <c r="B88" s="101"/>
+      <c r="C88" s="101"/>
+      <c r="D88" s="101"/>
+      <c r="E88" s="101"/>
       <c r="G88" s="80" t="s">
         <v>214</v>
       </c>
-      <c r="H88" s="97"/>
+      <c r="H88" s="101"/>
       <c r="I88" s="81" t="s">
         <v>708</v>
       </c>
@@ -51483,64 +51698,64 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="96" t="s">
+      <c r="A89" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B89" s="96" t="s">
+      <c r="B89" s="116" t="s">
         <v>172</v>
       </c>
-      <c r="C89" s="123" t="s">
+      <c r="C89" s="121" t="s">
         <v>710</v>
       </c>
-      <c r="D89" s="117" t="s">
+      <c r="D89" s="122" t="s">
         <v>711</v>
       </c>
-      <c r="E89" s="124" t="s">
+      <c r="E89" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F89" s="158" t="s">
+      <c r="F89" s="134" t="s">
         <v>712</v>
       </c>
-      <c r="G89" s="94"/>
-      <c r="H89" s="124" t="s">
+      <c r="G89" s="110"/>
+      <c r="H89" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I89" s="125" t="s">
+      <c r="I89" s="109" t="s">
         <v>713</v>
       </c>
-      <c r="J89" s="94"/>
+      <c r="J89" s="110"/>
     </row>
     <row r="90" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="147"/>
-      <c r="B90" s="147"/>
-      <c r="C90" s="147"/>
-      <c r="D90" s="147"/>
-      <c r="E90" s="147"/>
-      <c r="F90" s="159" t="s">
+      <c r="A90" s="117"/>
+      <c r="B90" s="117"/>
+      <c r="C90" s="117"/>
+      <c r="D90" s="117"/>
+      <c r="E90" s="117"/>
+      <c r="F90" s="135" t="s">
         <v>714</v>
       </c>
-      <c r="G90" s="94"/>
-      <c r="H90" s="147"/>
-      <c r="I90" s="160" t="s">
+      <c r="G90" s="110"/>
+      <c r="H90" s="117"/>
+      <c r="I90" s="154" t="s">
         <v>715</v>
       </c>
-      <c r="J90" s="161" t="s">
+      <c r="J90" s="155" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="97"/>
-      <c r="B91" s="97"/>
-      <c r="C91" s="97"/>
-      <c r="D91" s="97"/>
-      <c r="E91" s="97"/>
-      <c r="F91" s="151" t="s">
+      <c r="A91" s="101"/>
+      <c r="B91" s="101"/>
+      <c r="C91" s="101"/>
+      <c r="D91" s="101"/>
+      <c r="E91" s="101"/>
+      <c r="F91" s="136" t="s">
         <v>717</v>
       </c>
-      <c r="G91" s="94"/>
-      <c r="H91" s="97"/>
-      <c r="I91" s="97"/>
-      <c r="J91" s="97"/>
+      <c r="G91" s="110"/>
+      <c r="H91" s="101"/>
+      <c r="I91" s="101"/>
+      <c r="J91" s="101"/>
     </row>
     <row r="92" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="24" t="s">
@@ -51567,10 +51782,10 @@
       <c r="H92" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="I92" s="109" t="s">
+      <c r="I92" s="130" t="s">
         <v>722</v>
       </c>
-      <c r="J92" s="94"/>
+      <c r="J92" s="110"/>
     </row>
     <row r="93" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="24" t="s">
@@ -51629,110 +51844,110 @@
       <c r="H94" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="I94" s="138" t="s">
+      <c r="I94" s="114" t="s">
         <v>733</v>
       </c>
-      <c r="J94" s="94"/>
+      <c r="J94" s="110"/>
     </row>
     <row r="95" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="96" t="s">
+      <c r="A95" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B95" s="96" t="s">
+      <c r="B95" s="116" t="s">
         <v>179</v>
       </c>
-      <c r="C95" s="108" t="s">
+      <c r="C95" s="102" t="s">
         <v>734</v>
       </c>
-      <c r="D95" s="98" t="s">
+      <c r="D95" s="112" t="s">
         <v>735</v>
       </c>
       <c r="E95" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F95" s="103" t="s">
+      <c r="F95" s="104" t="s">
         <v>736</v>
       </c>
-      <c r="G95" s="95"/>
+      <c r="G95" s="105"/>
       <c r="H95" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I95" s="149" t="s">
+      <c r="I95" s="141" t="s">
         <v>737</v>
       </c>
-      <c r="J95" s="94"/>
+      <c r="J95" s="110"/>
     </row>
     <row r="96" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="97"/>
-      <c r="B96" s="97"/>
-      <c r="C96" s="97"/>
-      <c r="D96" s="97"/>
-      <c r="E96" s="97"/>
-      <c r="F96" s="104"/>
-      <c r="G96" s="105"/>
-      <c r="H96" s="97"/>
-      <c r="I96" s="162" t="s">
+      <c r="A96" s="101"/>
+      <c r="B96" s="101"/>
+      <c r="C96" s="101"/>
+      <c r="D96" s="101"/>
+      <c r="E96" s="101"/>
+      <c r="F96" s="106"/>
+      <c r="G96" s="107"/>
+      <c r="H96" s="101"/>
+      <c r="I96" s="142" t="s">
         <v>738</v>
       </c>
-      <c r="J96" s="94"/>
+      <c r="J96" s="110"/>
     </row>
     <row r="97" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="96" t="s">
+      <c r="A97" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B97" s="96" t="s">
+      <c r="B97" s="116" t="s">
         <v>179</v>
       </c>
-      <c r="C97" s="115" t="s">
+      <c r="C97" s="150" t="s">
         <v>739</v>
       </c>
-      <c r="D97" s="108" t="s">
+      <c r="D97" s="102" t="s">
         <v>740</v>
       </c>
       <c r="E97" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F97" s="108" t="s">
+      <c r="F97" s="102" t="s">
         <v>741</v>
       </c>
       <c r="G97" s="28"/>
       <c r="H97" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I97" s="162" t="s">
+      <c r="I97" s="142" t="s">
         <v>742</v>
       </c>
-      <c r="J97" s="94"/>
+      <c r="J97" s="110"/>
     </row>
     <row r="98" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="97"/>
-      <c r="B98" s="97"/>
-      <c r="C98" s="97"/>
-      <c r="D98" s="97"/>
-      <c r="E98" s="97"/>
-      <c r="F98" s="97"/>
+      <c r="A98" s="101"/>
+      <c r="B98" s="101"/>
+      <c r="C98" s="101"/>
+      <c r="D98" s="101"/>
+      <c r="E98" s="101"/>
+      <c r="F98" s="101"/>
       <c r="G98" s="74"/>
-      <c r="H98" s="97"/>
-      <c r="I98" s="149" t="s">
+      <c r="H98" s="101"/>
+      <c r="I98" s="141" t="s">
         <v>743</v>
       </c>
-      <c r="J98" s="94"/>
+      <c r="J98" s="110"/>
     </row>
     <row r="99" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="96" t="s">
+      <c r="A99" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="B99" s="96" t="s">
+      <c r="B99" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="C99" s="148" t="s">
+      <c r="C99" s="164" t="s">
         <v>744</v>
       </c>
-      <c r="D99" s="94"/>
+      <c r="D99" s="110"/>
       <c r="E99" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F99" s="177" t="s">
+      <c r="F99" s="137" t="s">
         <v>745</v>
       </c>
       <c r="G99" s="76" t="s">
@@ -51744,25 +51959,25 @@
       <c r="I99" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="J99" s="96"/>
+      <c r="J99" s="116"/>
     </row>
     <row r="100" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="97"/>
-      <c r="B100" s="97"/>
-      <c r="C100" s="149" t="s">
+      <c r="A100" s="101"/>
+      <c r="B100" s="101"/>
+      <c r="C100" s="141" t="s">
         <v>747</v>
       </c>
-      <c r="D100" s="94"/>
-      <c r="E100" s="97"/>
-      <c r="F100" s="97"/>
+      <c r="D100" s="110"/>
+      <c r="E100" s="101"/>
+      <c r="F100" s="101"/>
       <c r="G100" s="30" t="s">
         <v>748</v>
       </c>
-      <c r="H100" s="97"/>
+      <c r="H100" s="101"/>
       <c r="I100" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="J100" s="97"/>
+      <c r="J100" s="101"/>
     </row>
     <row r="101" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="24" t="s">
@@ -51780,10 +51995,10 @@
       <c r="E101" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="F101" s="109" t="s">
+      <c r="F101" s="130" t="s">
         <v>751</v>
       </c>
-      <c r="G101" s="94"/>
+      <c r="G101" s="110"/>
       <c r="H101" s="25" t="s">
         <v>175</v>
       </c>
@@ -51795,20 +52010,20 @@
       </c>
     </row>
     <row r="102" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="96" t="s">
+      <c r="A102" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="B102" s="96" t="s">
+      <c r="B102" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="C102" s="148" t="s">
+      <c r="C102" s="164" t="s">
         <v>754</v>
       </c>
-      <c r="D102" s="94"/>
+      <c r="D102" s="110"/>
       <c r="E102" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F102" s="150" t="s">
+      <c r="F102" s="131" t="s">
         <v>755</v>
       </c>
       <c r="G102" s="30" t="s">
@@ -51817,53 +52032,53 @@
       <c r="H102" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I102" s="103" t="s">
+      <c r="I102" s="104" t="s">
         <v>757</v>
       </c>
-      <c r="J102" s="95"/>
+      <c r="J102" s="105"/>
     </row>
     <row r="103" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="97"/>
-      <c r="B103" s="97"/>
-      <c r="C103" s="149" t="s">
+      <c r="A103" s="101"/>
+      <c r="B103" s="101"/>
+      <c r="C103" s="141" t="s">
         <v>758</v>
       </c>
-      <c r="D103" s="94"/>
-      <c r="E103" s="97"/>
-      <c r="F103" s="97"/>
+      <c r="D103" s="110"/>
+      <c r="E103" s="101"/>
+      <c r="F103" s="101"/>
       <c r="G103" s="76" t="s">
         <v>759</v>
       </c>
-      <c r="H103" s="97"/>
-      <c r="I103" s="104"/>
-      <c r="J103" s="105"/>
+      <c r="H103" s="101"/>
+      <c r="I103" s="106"/>
+      <c r="J103" s="107"/>
     </row>
     <row r="104" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="96" t="s">
+      <c r="A104" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B104" s="96" t="s">
+      <c r="B104" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="C104" s="150" t="s">
+      <c r="C104" s="131" t="s">
         <v>760</v>
       </c>
-      <c r="D104" s="137" t="s">
+      <c r="D104" s="163" t="s">
         <v>761</v>
       </c>
       <c r="E104" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F104" s="179" t="s">
+      <c r="F104" s="115" t="s">
         <v>762</v>
       </c>
-      <c r="G104" s="180" t="s">
+      <c r="G104" s="132" t="s">
         <v>763</v>
       </c>
       <c r="H104" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I104" s="166" t="s">
+      <c r="I104" s="153" t="s">
         <v>764</v>
       </c>
       <c r="J104" s="36" t="s">
@@ -51871,15 +52086,15 @@
       </c>
     </row>
     <row r="105" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="97"/>
-      <c r="B105" s="97"/>
-      <c r="C105" s="97"/>
-      <c r="D105" s="97"/>
-      <c r="E105" s="97"/>
-      <c r="F105" s="97"/>
-      <c r="G105" s="97"/>
-      <c r="H105" s="97"/>
-      <c r="I105" s="97"/>
+      <c r="A105" s="101"/>
+      <c r="B105" s="101"/>
+      <c r="C105" s="101"/>
+      <c r="D105" s="101"/>
+      <c r="E105" s="101"/>
+      <c r="F105" s="101"/>
+      <c r="G105" s="101"/>
+      <c r="H105" s="101"/>
+      <c r="I105" s="101"/>
       <c r="J105" s="33" t="s">
         <v>214</v>
       </c>
@@ -51909,79 +52124,79 @@
       <c r="H106" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="I106" s="138" t="s">
+      <c r="I106" s="114" t="s">
         <v>769</v>
       </c>
-      <c r="J106" s="94"/>
+      <c r="J106" s="110"/>
     </row>
     <row r="107" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="96" t="s">
+      <c r="A107" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="B107" s="96" t="s">
+      <c r="B107" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="C107" s="127" t="s">
+      <c r="C107" s="139" t="s">
         <v>770</v>
       </c>
-      <c r="D107" s="94"/>
-      <c r="E107" s="124" t="s">
+      <c r="D107" s="110"/>
+      <c r="E107" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F107" s="168" t="s">
+      <c r="F107" s="133" t="s">
         <v>771</v>
       </c>
-      <c r="G107" s="181" t="s">
+      <c r="G107" s="124" t="s">
         <v>772</v>
       </c>
-      <c r="H107" s="124" t="s">
+      <c r="H107" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I107" s="167" t="s">
+      <c r="I107" s="123" t="s">
         <v>773</v>
       </c>
-      <c r="J107" s="144" t="s">
+      <c r="J107" s="119" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="97"/>
-      <c r="B108" s="97"/>
-      <c r="C108" s="151" t="s">
+      <c r="A108" s="101"/>
+      <c r="B108" s="101"/>
+      <c r="C108" s="136" t="s">
         <v>775</v>
       </c>
-      <c r="D108" s="94"/>
-      <c r="E108" s="97"/>
-      <c r="F108" s="97"/>
-      <c r="G108" s="97"/>
-      <c r="H108" s="97"/>
-      <c r="I108" s="97"/>
-      <c r="J108" s="97"/>
+      <c r="D108" s="110"/>
+      <c r="E108" s="101"/>
+      <c r="F108" s="101"/>
+      <c r="G108" s="101"/>
+      <c r="H108" s="101"/>
+      <c r="I108" s="101"/>
+      <c r="J108" s="101"/>
     </row>
     <row r="109" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="96" t="s">
+      <c r="A109" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="B109" s="96" t="s">
+      <c r="B109" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="C109" s="151" t="s">
+      <c r="C109" s="136" t="s">
         <v>776</v>
       </c>
-      <c r="D109" s="94"/>
-      <c r="E109" s="124" t="s">
+      <c r="D109" s="110"/>
+      <c r="E109" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F109" s="154" t="s">
+      <c r="F109" s="125" t="s">
         <v>777</v>
       </c>
-      <c r="G109" s="178" t="s">
+      <c r="G109" s="108" t="s">
         <v>778</v>
       </c>
-      <c r="H109" s="124" t="s">
+      <c r="H109" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I109" s="168" t="s">
+      <c r="I109" s="133" t="s">
         <v>779</v>
       </c>
       <c r="J109" s="79" t="s">
@@ -51989,104 +52204,104 @@
       </c>
     </row>
     <row r="110" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="97"/>
-      <c r="B110" s="97"/>
-      <c r="C110" s="127" t="s">
+      <c r="A110" s="101"/>
+      <c r="B110" s="101"/>
+      <c r="C110" s="139" t="s">
         <v>780</v>
       </c>
-      <c r="D110" s="94"/>
-      <c r="E110" s="97"/>
-      <c r="F110" s="97"/>
-      <c r="G110" s="97"/>
-      <c r="H110" s="97"/>
-      <c r="I110" s="97"/>
+      <c r="D110" s="110"/>
+      <c r="E110" s="101"/>
+      <c r="F110" s="101"/>
+      <c r="G110" s="101"/>
+      <c r="H110" s="101"/>
+      <c r="I110" s="101"/>
       <c r="J110" s="80" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="96" t="s">
+      <c r="A111" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="B111" s="96" t="s">
+      <c r="B111" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="C111" s="152" t="s">
+      <c r="C111" s="148" t="s">
         <v>781</v>
       </c>
-      <c r="D111" s="94"/>
-      <c r="E111" s="124" t="s">
+      <c r="D111" s="110"/>
+      <c r="E111" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F111" s="178" t="s">
+      <c r="F111" s="108" t="s">
         <v>782</v>
       </c>
-      <c r="G111" s="167" t="s">
+      <c r="G111" s="123" t="s">
         <v>783</v>
       </c>
-      <c r="H111" s="124" t="s">
+      <c r="H111" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I111" s="153" t="s">
+      <c r="I111" s="147" t="s">
         <v>784</v>
       </c>
-      <c r="J111" s="94"/>
+      <c r="J111" s="110"/>
     </row>
     <row r="112" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="97"/>
-      <c r="B112" s="97"/>
-      <c r="C112" s="153" t="s">
+      <c r="A112" s="101"/>
+      <c r="B112" s="101"/>
+      <c r="C112" s="147" t="s">
         <v>785</v>
       </c>
-      <c r="D112" s="94"/>
-      <c r="E112" s="97"/>
-      <c r="F112" s="97"/>
-      <c r="G112" s="97"/>
-      <c r="H112" s="97"/>
-      <c r="I112" s="152" t="s">
+      <c r="D112" s="110"/>
+      <c r="E112" s="101"/>
+      <c r="F112" s="101"/>
+      <c r="G112" s="101"/>
+      <c r="H112" s="101"/>
+      <c r="I112" s="148" t="s">
         <v>786</v>
       </c>
-      <c r="J112" s="94"/>
+      <c r="J112" s="110"/>
     </row>
     <row r="113" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="96" t="s">
+      <c r="A113" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B113" s="96" t="s">
+      <c r="B113" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="C113" s="154" t="s">
+      <c r="C113" s="125" t="s">
         <v>787</v>
       </c>
-      <c r="D113" s="178" t="s">
+      <c r="D113" s="108" t="s">
         <v>788</v>
       </c>
-      <c r="E113" s="124" t="s">
+      <c r="E113" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F113" s="181" t="s">
+      <c r="F113" s="124" t="s">
         <v>789</v>
       </c>
-      <c r="G113" s="167" t="s">
+      <c r="G113" s="123" t="s">
         <v>790</v>
       </c>
-      <c r="H113" s="124" t="s">
+      <c r="H113" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="I113" s="125" t="s">
+      <c r="I113" s="109" t="s">
         <v>791</v>
       </c>
-      <c r="J113" s="94"/>
+      <c r="J113" s="110"/>
     </row>
     <row r="114" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="97"/>
-      <c r="B114" s="97"/>
-      <c r="C114" s="97"/>
-      <c r="D114" s="97"/>
-      <c r="E114" s="97"/>
-      <c r="F114" s="97"/>
-      <c r="G114" s="97"/>
-      <c r="H114" s="97"/>
+      <c r="A114" s="101"/>
+      <c r="B114" s="101"/>
+      <c r="C114" s="101"/>
+      <c r="D114" s="101"/>
+      <c r="E114" s="101"/>
+      <c r="F114" s="101"/>
+      <c r="G114" s="101"/>
+      <c r="H114" s="101"/>
       <c r="I114" s="82" t="s">
         <v>792</v>
       </c>
@@ -52095,77 +52310,77 @@
       </c>
     </row>
     <row r="115" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="96" t="s">
+      <c r="A115" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B115" s="96" t="s">
+      <c r="B115" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="C115" s="125" t="s">
+      <c r="C115" s="109" t="s">
         <v>794</v>
       </c>
-      <c r="D115" s="94"/>
-      <c r="E115" s="124" t="s">
+      <c r="D115" s="110"/>
+      <c r="E115" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="F115" s="154" t="s">
+      <c r="F115" s="125" t="s">
         <v>795</v>
       </c>
-      <c r="G115" s="181" t="s">
+      <c r="G115" s="124" t="s">
         <v>796</v>
       </c>
-      <c r="H115" s="124" t="s">
+      <c r="H115" s="120" t="s">
         <v>175</v>
       </c>
       <c r="I115" s="80" t="s">
         <v>214</v>
       </c>
-      <c r="J115" s="163"/>
+      <c r="J115" s="149"/>
     </row>
     <row r="116" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="97"/>
-      <c r="B116" s="97"/>
+      <c r="A116" s="101"/>
+      <c r="B116" s="101"/>
       <c r="C116" s="81" t="s">
         <v>797</v>
       </c>
       <c r="D116" s="82" t="s">
         <v>798</v>
       </c>
-      <c r="E116" s="97"/>
-      <c r="F116" s="97"/>
-      <c r="G116" s="97"/>
-      <c r="H116" s="97"/>
+      <c r="E116" s="101"/>
+      <c r="F116" s="101"/>
+      <c r="G116" s="101"/>
+      <c r="H116" s="101"/>
       <c r="I116" s="79" t="s">
         <v>223</v>
       </c>
-      <c r="J116" s="97"/>
+      <c r="J116" s="101"/>
     </row>
     <row r="117" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="96" t="s">
+      <c r="A117" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="B117" s="96" t="s">
+      <c r="B117" s="116" t="s">
         <v>207</v>
       </c>
-      <c r="C117" s="174" t="s">
+      <c r="C117" s="111" t="s">
         <v>799</v>
       </c>
-      <c r="D117" s="98" t="s">
+      <c r="D117" s="112" t="s">
         <v>800</v>
       </c>
       <c r="E117" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F117" s="171" t="s">
+      <c r="F117" s="128" t="s">
         <v>801</v>
       </c>
-      <c r="G117" s="179" t="s">
+      <c r="G117" s="115" t="s">
         <v>802</v>
       </c>
       <c r="H117" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I117" s="115" t="s">
+      <c r="I117" s="150" t="s">
         <v>803</v>
       </c>
       <c r="J117" s="33" t="s">
@@ -52173,15 +52388,15 @@
       </c>
     </row>
     <row r="118" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="97"/>
-      <c r="B118" s="97"/>
-      <c r="C118" s="97"/>
-      <c r="D118" s="97"/>
-      <c r="E118" s="97"/>
-      <c r="F118" s="97"/>
-      <c r="G118" s="97"/>
-      <c r="H118" s="97"/>
-      <c r="I118" s="97"/>
+      <c r="A118" s="101"/>
+      <c r="B118" s="101"/>
+      <c r="C118" s="101"/>
+      <c r="D118" s="101"/>
+      <c r="E118" s="101"/>
+      <c r="F118" s="101"/>
+      <c r="G118" s="101"/>
+      <c r="H118" s="101"/>
+      <c r="I118" s="101"/>
       <c r="J118" s="86" t="s">
         <v>804</v>
       </c>
@@ -52193,10 +52408,10 @@
       <c r="B119" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="C119" s="139" t="s">
+      <c r="C119" s="113" t="s">
         <v>805</v>
       </c>
-      <c r="D119" s="94"/>
+      <c r="D119" s="110"/>
       <c r="E119" s="25" t="s">
         <v>169</v>
       </c>
@@ -52209,10 +52424,10 @@
       <c r="H119" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="I119" s="164" t="s">
+      <c r="I119" s="151" t="s">
         <v>808</v>
       </c>
-      <c r="J119" s="94"/>
+      <c r="J119" s="110"/>
     </row>
     <row r="120" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="24" t="s">
@@ -52221,10 +52436,10 @@
       <c r="B120" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="C120" s="138" t="s">
+      <c r="C120" s="114" t="s">
         <v>809</v>
       </c>
-      <c r="D120" s="94"/>
+      <c r="D120" s="110"/>
       <c r="E120" s="25" t="s">
         <v>169</v>
       </c>
@@ -52243,25 +52458,25 @@
       <c r="J120" s="87"/>
     </row>
     <row r="121" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="96" t="s">
+      <c r="A121" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="B121" s="96" t="s">
+      <c r="B121" s="116" t="s">
         <v>207</v>
       </c>
-      <c r="C121" s="179" t="s">
+      <c r="C121" s="115" t="s">
         <v>813</v>
       </c>
-      <c r="D121" s="182" t="s">
+      <c r="D121" s="103" t="s">
         <v>814</v>
       </c>
       <c r="E121" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F121" s="98" t="s">
+      <c r="F121" s="112" t="s">
         <v>815</v>
       </c>
-      <c r="G121" s="174" t="s">
+      <c r="G121" s="111" t="s">
         <v>816</v>
       </c>
       <c r="H121" s="100" t="s">
@@ -52275,14 +52490,14 @@
       </c>
     </row>
     <row r="122" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="97"/>
-      <c r="B122" s="97"/>
-      <c r="C122" s="97"/>
-      <c r="D122" s="97"/>
-      <c r="E122" s="97"/>
-      <c r="F122" s="97"/>
-      <c r="G122" s="97"/>
-      <c r="H122" s="97"/>
+      <c r="A122" s="101"/>
+      <c r="B122" s="101"/>
+      <c r="C122" s="101"/>
+      <c r="D122" s="101"/>
+      <c r="E122" s="101"/>
+      <c r="F122" s="101"/>
+      <c r="G122" s="101"/>
+      <c r="H122" s="101"/>
       <c r="I122" s="30" t="s">
         <v>818</v>
       </c>
@@ -52291,20 +52506,20 @@
       </c>
     </row>
     <row r="123" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="96" t="s">
+      <c r="A123" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="B123" s="96" t="s">
+      <c r="B123" s="116" t="s">
         <v>207</v>
       </c>
-      <c r="C123" s="103" t="s">
+      <c r="C123" s="104" t="s">
         <v>819</v>
       </c>
-      <c r="D123" s="95"/>
+      <c r="D123" s="105"/>
       <c r="E123" s="100" t="s">
         <v>169</v>
       </c>
-      <c r="F123" s="182" t="s">
+      <c r="F123" s="103" t="s">
         <v>820</v>
       </c>
       <c r="G123" s="30" t="s">
@@ -52313,307 +52528,192 @@
       <c r="H123" s="100" t="s">
         <v>175</v>
       </c>
-      <c r="I123" s="165" t="s">
+      <c r="I123" s="152" t="s">
         <v>822</v>
       </c>
-      <c r="J123" s="95"/>
+      <c r="J123" s="105"/>
     </row>
     <row r="124" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="97"/>
-      <c r="B124" s="97"/>
-      <c r="C124" s="104"/>
-      <c r="D124" s="105"/>
-      <c r="E124" s="97"/>
-      <c r="F124" s="97"/>
+      <c r="A124" s="101"/>
+      <c r="B124" s="101"/>
+      <c r="C124" s="106"/>
+      <c r="D124" s="107"/>
+      <c r="E124" s="101"/>
+      <c r="F124" s="101"/>
       <c r="G124" s="72" t="s">
         <v>823</v>
       </c>
-      <c r="H124" s="97"/>
-      <c r="I124" s="104"/>
-      <c r="J124" s="105"/>
+      <c r="H124" s="101"/>
+      <c r="I124" s="106"/>
+      <c r="J124" s="107"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J124" xr:uid="{00000000-0009-0000-0000-000018000000}"/>
   <mergeCells count="470">
-    <mergeCell ref="E97:E98"/>
-    <mergeCell ref="F97:F98"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="C123:D124"/>
-    <mergeCell ref="D113:D114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="D117:D118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="A81:A83"/>
-    <mergeCell ref="A84:A86"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="D84:D86"/>
-    <mergeCell ref="E84:E86"/>
-    <mergeCell ref="F84:F86"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="D89:D91"/>
-    <mergeCell ref="F111:F112"/>
-    <mergeCell ref="G111:G112"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="F113:F114"/>
-    <mergeCell ref="G113:G114"/>
-    <mergeCell ref="H113:H114"/>
-    <mergeCell ref="F115:F116"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="B71:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="D74:D76"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="C78:C80"/>
-    <mergeCell ref="D78:D80"/>
-    <mergeCell ref="F78:F80"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="C81:C83"/>
-    <mergeCell ref="D81:D83"/>
-    <mergeCell ref="E81:E83"/>
-    <mergeCell ref="F81:F83"/>
-    <mergeCell ref="G115:G116"/>
-    <mergeCell ref="H115:H116"/>
-    <mergeCell ref="F117:F118"/>
-    <mergeCell ref="G117:G118"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="F121:F122"/>
-    <mergeCell ref="G121:G122"/>
-    <mergeCell ref="H121:H122"/>
-    <mergeCell ref="F123:F124"/>
-    <mergeCell ref="H123:H124"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="F102:F103"/>
-    <mergeCell ref="H102:H103"/>
-    <mergeCell ref="G109:G110"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="F104:F105"/>
-    <mergeCell ref="G104:G105"/>
-    <mergeCell ref="H104:H105"/>
-    <mergeCell ref="F107:F108"/>
-    <mergeCell ref="G107:G108"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="F109:F110"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="H89:H91"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F95:G96"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="G84:G86"/>
-    <mergeCell ref="H84:H86"/>
-    <mergeCell ref="G81:G83"/>
-    <mergeCell ref="H81:H83"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:H76"/>
-    <mergeCell ref="I74:I76"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="I71:I73"/>
-    <mergeCell ref="E71:E73"/>
-    <mergeCell ref="E74:E76"/>
-    <mergeCell ref="E78:E80"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="C65:C67"/>
-    <mergeCell ref="D65:D67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A78:A80"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="F63:F64"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="E68:E70"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E65:E67"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="I111:J111"/>
-    <mergeCell ref="I112:J112"/>
-    <mergeCell ref="I113:J113"/>
-    <mergeCell ref="J115:J116"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="I119:J119"/>
-    <mergeCell ref="I123:J124"/>
-    <mergeCell ref="J99:J100"/>
-    <mergeCell ref="I102:J103"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="I106:J106"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="J107:J108"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="I90:I91"/>
-    <mergeCell ref="J90:J91"/>
-    <mergeCell ref="I92:J92"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H65:H67"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="I66:I67"/>
-    <mergeCell ref="J66:J67"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="H68:H70"/>
-    <mergeCell ref="I68:I70"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="G59:G60"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="F59:F60"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="G57:G58"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="I57:J58"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="E115:E116"/>
-    <mergeCell ref="E117:E118"/>
-    <mergeCell ref="E121:E122"/>
-    <mergeCell ref="E123:E124"/>
-    <mergeCell ref="E99:E100"/>
-    <mergeCell ref="E102:E103"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="E107:E108"/>
-    <mergeCell ref="E109:E110"/>
-    <mergeCell ref="E111:E112"/>
-    <mergeCell ref="E113:E114"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="E89:E91"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:D96"/>
-    <mergeCell ref="E95:E96"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:J23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="I43:J44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="I45:J46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="F3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="H45:H46"/>
@@ -52636,175 +52736,290 @@
     <mergeCell ref="E45:E46"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B47:B48"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:D96"/>
+    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="E123:E124"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="E107:E108"/>
+    <mergeCell ref="E109:E110"/>
+    <mergeCell ref="E111:E112"/>
+    <mergeCell ref="E113:E114"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="E115:E116"/>
+    <mergeCell ref="E117:E118"/>
+    <mergeCell ref="E121:E122"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="E89:E91"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="A55:A56"/>
     <mergeCell ref="H53:H54"/>
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="I43:J44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="I45:J46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I22:J23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:G16"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="G59:G60"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="F59:F60"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="G57:G58"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="I57:J58"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="I111:J111"/>
+    <mergeCell ref="I112:J112"/>
+    <mergeCell ref="I113:J113"/>
+    <mergeCell ref="J115:J116"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="I119:J119"/>
+    <mergeCell ref="I123:J124"/>
+    <mergeCell ref="J99:J100"/>
+    <mergeCell ref="I102:J103"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="I106:J106"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="J107:J108"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="F63:F64"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="E68:E70"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E65:E67"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="I90:I91"/>
+    <mergeCell ref="J90:J91"/>
+    <mergeCell ref="I92:J92"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="I66:I67"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="E71:E73"/>
+    <mergeCell ref="E74:E76"/>
+    <mergeCell ref="E78:E80"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="C65:C67"/>
+    <mergeCell ref="D65:D67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="I74:I76"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="I71:I73"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="I68:I70"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="G84:G86"/>
+    <mergeCell ref="H84:H86"/>
+    <mergeCell ref="G81:G83"/>
+    <mergeCell ref="H81:H83"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="H89:H91"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F95:G96"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="F78:F80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="C81:C83"/>
+    <mergeCell ref="D81:D83"/>
+    <mergeCell ref="E81:E83"/>
+    <mergeCell ref="F81:F83"/>
+    <mergeCell ref="G115:G116"/>
+    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="F117:F118"/>
+    <mergeCell ref="G117:G118"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="G109:G110"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="F104:F105"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="H104:H105"/>
+    <mergeCell ref="F107:F108"/>
+    <mergeCell ref="G107:G108"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="F109:F110"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="C78:C80"/>
+    <mergeCell ref="D78:D80"/>
+    <mergeCell ref="A81:A83"/>
+    <mergeCell ref="A84:A86"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="D84:D86"/>
+    <mergeCell ref="E84:E86"/>
+    <mergeCell ref="F84:F86"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="E97:E98"/>
+    <mergeCell ref="F97:F98"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="C123:D124"/>
+    <mergeCell ref="D113:D114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="D117:D118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C121:C122"/>
+    <mergeCell ref="F111:F112"/>
+    <mergeCell ref="G111:G112"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="F113:F114"/>
+    <mergeCell ref="G113:G114"/>
+    <mergeCell ref="H113:H114"/>
+    <mergeCell ref="F115:F116"/>
+    <mergeCell ref="F121:F122"/>
+    <mergeCell ref="G121:G122"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="F123:F124"/>
+    <mergeCell ref="H123:H124"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -55574,2746 +55789,2746 @@
   <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8" style="183" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" style="183" customWidth="1"/>
-    <col min="3" max="3" width="31.5" style="183" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="183" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="23" style="183" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" style="183" customWidth="1"/>
-    <col min="7" max="7" width="14.5" style="183" customWidth="1"/>
-    <col min="8" max="9" width="17.33203125" style="183" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" style="183" customWidth="1"/>
-    <col min="11" max="11" width="85.83203125" style="183" customWidth="1"/>
-    <col min="12" max="16384" width="14.5" style="183"/>
+    <col min="1" max="1" width="8" style="94" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" style="94" customWidth="1"/>
+    <col min="3" max="3" width="31.5" style="94" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="94" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="23" style="94" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" style="94" customWidth="1"/>
+    <col min="7" max="7" width="14.5" style="94" customWidth="1"/>
+    <col min="8" max="9" width="17.33203125" style="94" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" style="94" customWidth="1"/>
+    <col min="11" max="11" width="85.83203125" style="94" customWidth="1"/>
+    <col min="12" max="16384" width="14.5" style="94"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="186" t="s">
+      <c r="B1" s="97" t="s">
         <v>824</v>
       </c>
-      <c r="C1" s="186" t="s">
+      <c r="C1" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="186" t="s">
+      <c r="D1" s="97" t="s">
         <v>892</v>
       </c>
-      <c r="E1" s="186" t="s">
+      <c r="E1" s="97" t="s">
         <v>825</v>
       </c>
-      <c r="F1" s="187" t="s">
+      <c r="F1" s="98" t="s">
         <v>893</v>
       </c>
-      <c r="G1" s="187" t="s">
+      <c r="G1" s="98" t="s">
         <v>894</v>
       </c>
-      <c r="H1" s="187" t="s">
+      <c r="H1" s="98" t="s">
         <v>895</v>
       </c>
-      <c r="I1" s="187" t="s">
+      <c r="I1" s="98" t="s">
         <v>896</v>
       </c>
-      <c r="J1" s="187" t="s">
+      <c r="J1" s="98" t="s">
         <v>897</v>
       </c>
-      <c r="K1" s="186" t="s">
+      <c r="K1" s="97" t="s">
         <v>898</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="150" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="185">
+      <c r="A2" s="96">
         <v>21</v>
       </c>
-      <c r="B2" s="184" t="s">
+      <c r="B2" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C2" s="184" t="s">
+      <c r="C2" s="95" t="s">
         <v>859</v>
       </c>
-      <c r="D2" s="184" t="s">
+      <c r="D2" s="95" t="s">
         <v>860</v>
       </c>
-      <c r="E2" s="184" t="s">
+      <c r="E2" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F2" s="185">
+      <c r="F2" s="96">
         <v>9</v>
       </c>
-      <c r="G2" s="185">
+      <c r="G2" s="96">
         <v>8</v>
       </c>
-      <c r="H2" s="185">
+      <c r="H2" s="96">
         <v>0</v>
       </c>
-      <c r="I2" s="185">
+      <c r="I2" s="96">
         <v>17</v>
       </c>
-      <c r="J2" s="185">
+      <c r="J2" s="96">
         <v>17</v>
       </c>
-      <c r="K2" s="184" t="s">
+      <c r="K2" s="95" t="s">
         <v>925</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="150" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="185">
+      <c r="A3" s="96">
         <v>25</v>
       </c>
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C3" s="184" t="s">
+      <c r="C3" s="95" t="s">
         <v>884</v>
       </c>
-      <c r="D3" s="184" t="s">
+      <c r="D3" s="95" t="s">
         <v>885</v>
       </c>
-      <c r="E3" s="184" t="s">
+      <c r="E3" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F3" s="185">
+      <c r="F3" s="96">
         <v>9</v>
       </c>
-      <c r="G3" s="185">
+      <c r="G3" s="96">
         <v>8</v>
       </c>
-      <c r="H3" s="185">
+      <c r="H3" s="96">
         <v>0</v>
       </c>
-      <c r="I3" s="185">
+      <c r="I3" s="96">
         <v>17</v>
       </c>
-      <c r="J3" s="185">
+      <c r="J3" s="96">
         <v>17</v>
       </c>
-      <c r="K3" s="184" t="s">
+      <c r="K3" s="95" t="s">
         <v>929</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="150" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="185">
+      <c r="A4" s="96">
         <v>26</v>
       </c>
-      <c r="B4" s="184" t="s">
+      <c r="B4" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C4" s="184" t="s">
+      <c r="C4" s="95" t="s">
         <v>621</v>
       </c>
-      <c r="D4" s="184" t="s">
+      <c r="D4" s="95" t="s">
         <v>620</v>
       </c>
-      <c r="E4" s="184" t="s">
+      <c r="E4" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F4" s="185">
+      <c r="F4" s="96">
         <v>9</v>
       </c>
-      <c r="G4" s="185">
+      <c r="G4" s="96">
         <v>8</v>
       </c>
-      <c r="H4" s="185">
+      <c r="H4" s="96">
         <v>0</v>
       </c>
-      <c r="I4" s="185">
+      <c r="I4" s="96">
         <v>17</v>
       </c>
-      <c r="J4" s="185">
+      <c r="J4" s="96">
         <v>17</v>
       </c>
-      <c r="K4" s="184" t="s">
+      <c r="K4" s="95" t="s">
         <v>930</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="185">
+      <c r="A5" s="96">
         <v>3</v>
       </c>
-      <c r="B5" s="184" t="s">
+      <c r="B5" s="95" t="s">
         <v>834</v>
       </c>
-      <c r="C5" s="184" t="s">
+      <c r="C5" s="95" t="s">
         <v>191</v>
       </c>
-      <c r="D5" s="184" t="s">
+      <c r="D5" s="95" t="s">
         <v>432</v>
       </c>
-      <c r="E5" s="184" t="s">
+      <c r="E5" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F5" s="185">
+      <c r="F5" s="96">
         <v>6</v>
       </c>
-      <c r="G5" s="185">
+      <c r="G5" s="96">
         <v>10</v>
       </c>
-      <c r="H5" s="185">
+      <c r="H5" s="96">
         <v>0</v>
       </c>
-      <c r="I5" s="185">
+      <c r="I5" s="96">
         <v>16</v>
       </c>
-      <c r="J5" s="185">
+      <c r="J5" s="96">
         <v>16</v>
       </c>
-      <c r="K5" s="184" t="s">
+      <c r="K5" s="95" t="s">
         <v>902</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="185">
+      <c r="A6" s="96">
         <v>7</v>
       </c>
-      <c r="B6" s="184" t="s">
+      <c r="B6" s="95" t="s">
         <v>834</v>
       </c>
-      <c r="C6" s="184" t="s">
+      <c r="C6" s="95" t="s">
         <v>542</v>
       </c>
-      <c r="D6" s="184" t="s">
+      <c r="D6" s="95" t="s">
         <v>541</v>
       </c>
-      <c r="E6" s="184" t="s">
+      <c r="E6" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="96">
         <v>6</v>
       </c>
-      <c r="G6" s="185">
+      <c r="G6" s="96">
         <v>10</v>
       </c>
-      <c r="H6" s="185">
+      <c r="H6" s="96">
         <v>0</v>
       </c>
-      <c r="I6" s="185">
+      <c r="I6" s="96">
         <v>16</v>
       </c>
-      <c r="J6" s="185">
+      <c r="J6" s="96">
         <v>16</v>
       </c>
-      <c r="K6" s="184" t="s">
+      <c r="K6" s="95" t="s">
         <v>908</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="185">
+      <c r="A7" s="96">
         <v>8</v>
       </c>
-      <c r="B7" s="184" t="s">
+      <c r="B7" s="95" t="s">
         <v>834</v>
       </c>
-      <c r="C7" s="184" t="s">
+      <c r="C7" s="95" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="184" t="s">
+      <c r="D7" s="95" t="s">
         <v>909</v>
       </c>
-      <c r="E7" s="184" t="s">
+      <c r="E7" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F7" s="185">
+      <c r="F7" s="96">
         <v>6</v>
       </c>
-      <c r="G7" s="185">
+      <c r="G7" s="96">
         <v>10</v>
       </c>
-      <c r="H7" s="185">
+      <c r="H7" s="96">
         <v>0</v>
       </c>
-      <c r="I7" s="185">
+      <c r="I7" s="96">
         <v>16</v>
       </c>
-      <c r="J7" s="185">
+      <c r="J7" s="96">
         <v>16</v>
       </c>
-      <c r="K7" s="184" t="s">
+      <c r="K7" s="95" t="s">
         <v>910</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="185">
+      <c r="A8" s="96">
         <v>9</v>
       </c>
-      <c r="B8" s="184" t="s">
+      <c r="B8" s="95" t="s">
         <v>834</v>
       </c>
-      <c r="C8" s="184" t="s">
+      <c r="C8" s="95" t="s">
         <v>244</v>
       </c>
-      <c r="D8" s="184" t="s">
+      <c r="D8" s="95" t="s">
         <v>243</v>
       </c>
-      <c r="E8" s="184" t="s">
+      <c r="E8" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F8" s="185">
+      <c r="F8" s="96">
         <v>6</v>
       </c>
-      <c r="G8" s="185">
+      <c r="G8" s="96">
         <v>10</v>
       </c>
-      <c r="H8" s="185">
+      <c r="H8" s="96">
         <v>0</v>
       </c>
-      <c r="I8" s="185">
+      <c r="I8" s="96">
         <v>16</v>
       </c>
-      <c r="J8" s="185">
+      <c r="J8" s="96">
         <v>16</v>
       </c>
-      <c r="K8" s="184" t="s">
+      <c r="K8" s="95" t="s">
         <v>911</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="185">
+      <c r="A9" s="96">
         <v>4</v>
       </c>
-      <c r="B9" s="184" t="s">
+      <c r="B9" s="95" t="s">
         <v>834</v>
       </c>
-      <c r="C9" s="184" t="s">
+      <c r="C9" s="95" t="s">
         <v>580</v>
       </c>
-      <c r="D9" s="184" t="s">
+      <c r="D9" s="95" t="s">
         <v>579</v>
       </c>
-      <c r="E9" s="184" t="s">
+      <c r="E9" s="95" t="s">
         <v>847</v>
       </c>
-      <c r="F9" s="185">
+      <c r="F9" s="96">
         <v>3</v>
       </c>
-      <c r="G9" s="185">
+      <c r="G9" s="96">
         <v>12</v>
       </c>
-      <c r="H9" s="185">
+      <c r="H9" s="96">
         <v>0</v>
       </c>
-      <c r="I9" s="185">
+      <c r="I9" s="96">
         <v>15</v>
       </c>
-      <c r="J9" s="185">
+      <c r="J9" s="96">
         <v>15</v>
       </c>
-      <c r="K9" s="184" t="s">
+      <c r="K9" s="95" t="s">
         <v>903</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="185">
+      <c r="A10" s="96">
         <v>5</v>
       </c>
-      <c r="B10" s="184" t="s">
+      <c r="B10" s="95" t="s">
         <v>834</v>
       </c>
-      <c r="C10" s="184" t="s">
+      <c r="C10" s="95" t="s">
         <v>849</v>
       </c>
-      <c r="D10" s="184" t="s">
+      <c r="D10" s="95" t="s">
         <v>904</v>
       </c>
-      <c r="E10" s="184" t="s">
+      <c r="E10" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F10" s="185">
+      <c r="F10" s="96">
         <v>3</v>
       </c>
-      <c r="G10" s="185">
+      <c r="G10" s="96">
         <v>12</v>
       </c>
-      <c r="H10" s="185">
+      <c r="H10" s="96">
         <v>0</v>
       </c>
-      <c r="I10" s="185">
+      <c r="I10" s="96">
         <v>15</v>
       </c>
-      <c r="J10" s="185">
+      <c r="J10" s="96">
         <v>15</v>
       </c>
-      <c r="K10" s="184" t="s">
+      <c r="K10" s="95" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="185">
+      <c r="A11" s="96">
         <v>6</v>
       </c>
-      <c r="B11" s="184" t="s">
+      <c r="B11" s="95" t="s">
         <v>834</v>
       </c>
-      <c r="C11" s="184" t="s">
+      <c r="C11" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="D11" s="184" t="s">
+      <c r="D11" s="95" t="s">
         <v>906</v>
       </c>
-      <c r="E11" s="184" t="s">
+      <c r="E11" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F11" s="185">
+      <c r="F11" s="96">
         <v>3</v>
       </c>
-      <c r="G11" s="185">
+      <c r="G11" s="96">
         <v>12</v>
       </c>
-      <c r="H11" s="185">
+      <c r="H11" s="96">
         <v>0</v>
       </c>
-      <c r="I11" s="185">
+      <c r="I11" s="96">
         <v>15</v>
       </c>
-      <c r="J11" s="185">
+      <c r="J11" s="96">
         <v>15</v>
       </c>
-      <c r="K11" s="184" t="s">
+      <c r="K11" s="95" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="120" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="185">
+      <c r="A12" s="96">
         <v>14</v>
       </c>
-      <c r="B12" s="184" t="s">
+      <c r="B12" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="184" t="s">
+      <c r="C12" s="95" t="s">
         <v>871</v>
       </c>
-      <c r="D12" s="184" t="s">
+      <c r="D12" s="95" t="s">
         <v>872</v>
       </c>
-      <c r="E12" s="184" t="s">
+      <c r="E12" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F12" s="185">
+      <c r="F12" s="96">
         <v>9</v>
       </c>
-      <c r="G12" s="185">
+      <c r="G12" s="96">
         <v>6</v>
       </c>
-      <c r="H12" s="185">
+      <c r="H12" s="96">
         <v>0</v>
       </c>
-      <c r="I12" s="185">
+      <c r="I12" s="96">
         <v>15</v>
       </c>
-      <c r="J12" s="185">
+      <c r="J12" s="96">
         <v>15</v>
       </c>
-      <c r="K12" s="184" t="s">
+      <c r="K12" s="95" t="s">
         <v>916</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="185">
+      <c r="A13" s="96">
         <v>18</v>
       </c>
-      <c r="B13" s="184" t="s">
+      <c r="B13" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C13" s="184" t="s">
+      <c r="C13" s="95" t="s">
         <v>274</v>
       </c>
-      <c r="D13" s="184" t="s">
+      <c r="D13" s="95" t="s">
         <v>273</v>
       </c>
-      <c r="E13" s="184" t="s">
+      <c r="E13" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F13" s="185">
+      <c r="F13" s="96">
         <v>9</v>
       </c>
-      <c r="G13" s="185">
+      <c r="G13" s="96">
         <v>6</v>
       </c>
-      <c r="H13" s="185">
+      <c r="H13" s="96">
         <v>0</v>
       </c>
-      <c r="I13" s="185">
+      <c r="I13" s="96">
         <v>15</v>
       </c>
-      <c r="J13" s="185">
+      <c r="J13" s="96">
         <v>15</v>
       </c>
-      <c r="K13" s="184" t="s">
+      <c r="K13" s="95" t="s">
         <v>922</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="185">
+      <c r="A14" s="96">
         <v>22</v>
       </c>
-      <c r="B14" s="184" t="s">
+      <c r="B14" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C14" s="184" t="s">
+      <c r="C14" s="95" t="s">
         <v>861</v>
       </c>
-      <c r="D14" s="184" t="s">
+      <c r="D14" s="95" t="s">
         <v>862</v>
       </c>
-      <c r="E14" s="184" t="s">
+      <c r="E14" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F14" s="185">
+      <c r="F14" s="96">
         <v>9</v>
       </c>
-      <c r="G14" s="185">
+      <c r="G14" s="96">
         <v>6</v>
       </c>
-      <c r="H14" s="185">
+      <c r="H14" s="96">
         <v>0</v>
       </c>
-      <c r="I14" s="185">
+      <c r="I14" s="96">
         <v>15</v>
       </c>
-      <c r="J14" s="185">
+      <c r="J14" s="96">
         <v>15</v>
       </c>
-      <c r="K14" s="184" t="s">
+      <c r="K14" s="95" t="s">
         <v>926</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="90" x14ac:dyDescent="0.2">
-      <c r="A15" s="185">
+      <c r="A15" s="96">
         <v>52</v>
       </c>
-      <c r="B15" s="184" t="s">
+      <c r="B15" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="C15" s="184" t="s">
+      <c r="C15" s="95" t="s">
         <v>613</v>
       </c>
-      <c r="D15" s="184" t="s">
+      <c r="D15" s="95" t="s">
         <v>612</v>
       </c>
-      <c r="E15" s="184" t="s">
+      <c r="E15" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F15" s="185">
+      <c r="F15" s="96">
         <v>9</v>
       </c>
-      <c r="G15" s="185">
+      <c r="G15" s="96">
         <v>0</v>
       </c>
-      <c r="H15" s="185">
+      <c r="H15" s="96">
         <v>6</v>
       </c>
-      <c r="I15" s="185">
+      <c r="I15" s="96">
         <v>15</v>
       </c>
-      <c r="J15" s="185">
+      <c r="J15" s="96">
         <v>15</v>
       </c>
-      <c r="K15" s="184" t="s">
+      <c r="K15" s="95" t="s">
         <v>955</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="150" x14ac:dyDescent="0.2">
-      <c r="A16" s="185">
+      <c r="A16" s="96">
         <v>53</v>
       </c>
-      <c r="B16" s="184" t="s">
+      <c r="B16" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="C16" s="184" t="s">
+      <c r="C16" s="95" t="s">
         <v>839</v>
       </c>
-      <c r="D16" s="184" t="s">
+      <c r="D16" s="95" t="s">
         <v>956</v>
       </c>
-      <c r="E16" s="184" t="s">
+      <c r="E16" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F16" s="185">
+      <c r="F16" s="96">
         <v>6</v>
       </c>
-      <c r="G16" s="185">
+      <c r="G16" s="96">
         <v>0</v>
       </c>
-      <c r="H16" s="185">
+      <c r="H16" s="96">
         <v>9</v>
       </c>
-      <c r="I16" s="185">
+      <c r="I16" s="96">
         <v>15</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="96">
         <v>15</v>
       </c>
-      <c r="K16" s="184" t="s">
+      <c r="K16" s="95" t="s">
         <v>958</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="185">
+      <c r="A17" s="96">
         <v>60</v>
       </c>
-      <c r="B17" s="184" t="s">
+      <c r="B17" s="95" t="s">
         <v>830</v>
       </c>
-      <c r="C17" s="184" t="s">
+      <c r="C17" s="95" t="s">
         <v>829</v>
       </c>
-      <c r="D17" s="184" t="s">
+      <c r="D17" s="95" t="s">
         <v>960</v>
       </c>
-      <c r="E17" s="184" t="s">
+      <c r="E17" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F17" s="185">
+      <c r="F17" s="96">
         <v>3</v>
       </c>
-      <c r="G17" s="185">
+      <c r="G17" s="96">
         <v>12</v>
       </c>
-      <c r="H17" s="185">
+      <c r="H17" s="96">
         <v>0</v>
       </c>
-      <c r="I17" s="185">
+      <c r="I17" s="96">
         <v>15</v>
       </c>
-      <c r="J17" s="185">
+      <c r="J17" s="96">
         <v>15</v>
       </c>
-      <c r="K17" s="184" t="s">
+      <c r="K17" s="95" t="s">
         <v>961</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="185">
+      <c r="A18" s="96">
         <v>62</v>
       </c>
-      <c r="B18" s="184" t="s">
+      <c r="B18" s="95" t="s">
         <v>830</v>
       </c>
-      <c r="C18" s="184" t="s">
+      <c r="C18" s="95" t="s">
         <v>626</v>
       </c>
-      <c r="D18" s="184" t="s">
+      <c r="D18" s="95" t="s">
         <v>625</v>
       </c>
-      <c r="E18" s="184" t="s">
+      <c r="E18" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F18" s="185">
+      <c r="F18" s="96">
         <v>3</v>
       </c>
-      <c r="G18" s="185">
+      <c r="G18" s="96">
         <v>12</v>
       </c>
-      <c r="H18" s="185">
+      <c r="H18" s="96">
         <v>0</v>
       </c>
-      <c r="I18" s="185">
+      <c r="I18" s="96">
         <v>15</v>
       </c>
-      <c r="J18" s="185">
+      <c r="J18" s="96">
         <v>15</v>
       </c>
-      <c r="K18" s="184" t="s">
+      <c r="K18" s="95" t="s">
         <v>964</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="185">
+      <c r="A19" s="96">
         <v>17</v>
       </c>
-      <c r="B19" s="184" t="s">
+      <c r="B19" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C19" s="184" t="s">
+      <c r="C19" s="95" t="s">
         <v>843</v>
       </c>
-      <c r="D19" s="184" t="s">
+      <c r="D19" s="95" t="s">
         <v>920</v>
       </c>
-      <c r="E19" s="184" t="s">
+      <c r="E19" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="F19" s="185">
+      <c r="F19" s="96">
         <v>6</v>
       </c>
-      <c r="G19" s="185">
+      <c r="G19" s="96">
         <v>8</v>
       </c>
-      <c r="H19" s="185">
+      <c r="H19" s="96">
         <v>0</v>
       </c>
-      <c r="I19" s="185">
+      <c r="I19" s="96">
         <v>14</v>
       </c>
-      <c r="J19" s="185">
+      <c r="J19" s="96">
         <v>14</v>
       </c>
-      <c r="K19" s="184" t="s">
+      <c r="K19" s="95" t="s">
         <v>921</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="135" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="185">
+      <c r="A20" s="96">
         <v>19</v>
       </c>
-      <c r="B20" s="184" t="s">
+      <c r="B20" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C20" s="184" t="s">
+      <c r="C20" s="95" t="s">
         <v>280</v>
       </c>
-      <c r="D20" s="184" t="s">
+      <c r="D20" s="95" t="s">
         <v>279</v>
       </c>
-      <c r="E20" s="184" t="s">
+      <c r="E20" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F20" s="185">
+      <c r="F20" s="96">
         <v>6</v>
       </c>
-      <c r="G20" s="185">
+      <c r="G20" s="96">
         <v>8</v>
       </c>
-      <c r="H20" s="185">
+      <c r="H20" s="96">
         <v>0</v>
       </c>
-      <c r="I20" s="185">
+      <c r="I20" s="96">
         <v>14</v>
       </c>
-      <c r="J20" s="185">
+      <c r="J20" s="96">
         <v>14</v>
       </c>
-      <c r="K20" s="184" t="s">
+      <c r="K20" s="95" t="s">
         <v>923</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="185">
+      <c r="A21" s="96">
         <v>20</v>
       </c>
-      <c r="B21" s="184" t="s">
+      <c r="B21" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C21" s="184" t="s">
+      <c r="C21" s="95" t="s">
         <v>546</v>
       </c>
-      <c r="D21" s="184" t="s">
+      <c r="D21" s="95" t="s">
         <v>545</v>
       </c>
-      <c r="E21" s="184" t="s">
+      <c r="E21" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F21" s="185">
+      <c r="F21" s="96">
         <v>6</v>
       </c>
-      <c r="G21" s="185">
+      <c r="G21" s="96">
         <v>8</v>
       </c>
-      <c r="H21" s="185">
+      <c r="H21" s="96">
         <v>0</v>
       </c>
-      <c r="I21" s="185">
+      <c r="I21" s="96">
         <v>14</v>
       </c>
-      <c r="J21" s="185">
+      <c r="J21" s="96">
         <v>14</v>
       </c>
-      <c r="K21" s="184" t="s">
+      <c r="K21" s="95" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="120" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="185">
+      <c r="A22" s="96">
         <v>23</v>
       </c>
-      <c r="B22" s="184" t="s">
+      <c r="B22" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C22" s="184" t="s">
+      <c r="C22" s="95" t="s">
         <v>583</v>
       </c>
-      <c r="D22" s="184" t="s">
+      <c r="D22" s="95" t="s">
         <v>582</v>
       </c>
-      <c r="E22" s="184" t="s">
+      <c r="E22" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F22" s="185">
+      <c r="F22" s="96">
         <v>6</v>
       </c>
-      <c r="G22" s="185">
+      <c r="G22" s="96">
         <v>8</v>
       </c>
-      <c r="H22" s="185">
+      <c r="H22" s="96">
         <v>0</v>
       </c>
-      <c r="I22" s="185">
+      <c r="I22" s="96">
         <v>14</v>
       </c>
-      <c r="J22" s="185">
+      <c r="J22" s="96">
         <v>14</v>
       </c>
-      <c r="K22" s="184" t="s">
+      <c r="K22" s="95" t="s">
         <v>927</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="185">
+      <c r="A23" s="96">
         <v>24</v>
       </c>
-      <c r="B23" s="184" t="s">
+      <c r="B23" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C23" s="184" t="s">
+      <c r="C23" s="95" t="s">
         <v>195</v>
       </c>
-      <c r="D23" s="184" t="s">
+      <c r="D23" s="95" t="s">
         <v>194</v>
       </c>
-      <c r="E23" s="184" t="s">
+      <c r="E23" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F23" s="185">
+      <c r="F23" s="96">
         <v>6</v>
       </c>
-      <c r="G23" s="185">
+      <c r="G23" s="96">
         <v>8</v>
       </c>
-      <c r="H23" s="185">
+      <c r="H23" s="96">
         <v>0</v>
       </c>
-      <c r="I23" s="185">
+      <c r="I23" s="96">
         <v>14</v>
       </c>
-      <c r="J23" s="185">
+      <c r="J23" s="96">
         <v>14</v>
       </c>
-      <c r="K23" s="184" t="s">
+      <c r="K23" s="95" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="120" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="185">
+      <c r="A24" s="96">
         <v>29</v>
       </c>
-      <c r="B24" s="184" t="s">
+      <c r="B24" s="95" t="s">
         <v>845</v>
       </c>
-      <c r="C24" s="184" t="s">
+      <c r="C24" s="95" t="s">
         <v>319</v>
       </c>
-      <c r="D24" s="184" t="s">
+      <c r="D24" s="95" t="s">
         <v>547</v>
       </c>
-      <c r="E24" s="184" t="s">
+      <c r="E24" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="F24" s="185">
+      <c r="F24" s="96">
         <v>2</v>
       </c>
-      <c r="G24" s="185">
+      <c r="G24" s="96">
         <v>12</v>
       </c>
-      <c r="H24" s="185">
+      <c r="H24" s="96">
         <v>0</v>
       </c>
-      <c r="I24" s="185">
+      <c r="I24" s="96">
         <v>14</v>
       </c>
-      <c r="J24" s="185">
+      <c r="J24" s="96">
         <v>14</v>
       </c>
-      <c r="K24" s="184" t="s">
+      <c r="K24" s="95" t="s">
         <v>934</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="135" x14ac:dyDescent="0.2">
-      <c r="A25" s="185">
+      <c r="A25" s="96">
         <v>51</v>
       </c>
-      <c r="B25" s="184" t="s">
+      <c r="B25" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="C25" s="184" t="s">
+      <c r="C25" s="95" t="s">
         <v>575</v>
       </c>
-      <c r="D25" s="184" t="s">
+      <c r="D25" s="95" t="s">
         <v>573</v>
       </c>
-      <c r="E25" s="184" t="s">
+      <c r="E25" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F25" s="185">
+      <c r="F25" s="96">
         <v>6</v>
       </c>
-      <c r="G25" s="185">
+      <c r="G25" s="96">
         <v>0</v>
       </c>
-      <c r="H25" s="185">
+      <c r="H25" s="96">
         <v>8</v>
       </c>
-      <c r="I25" s="185">
+      <c r="I25" s="96">
         <v>14</v>
       </c>
-      <c r="J25" s="185">
+      <c r="J25" s="96">
         <v>14</v>
       </c>
-      <c r="K25" s="184" t="s">
+      <c r="K25" s="95" t="s">
         <v>965</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="135" x14ac:dyDescent="0.2">
-      <c r="A26" s="185">
+      <c r="A26" s="96">
         <v>54</v>
       </c>
-      <c r="B26" s="184" t="s">
+      <c r="B26" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="C26" s="184" t="s">
+      <c r="C26" s="95" t="s">
         <v>842</v>
       </c>
-      <c r="D26" s="184" t="s">
+      <c r="D26" s="95" t="s">
         <v>966</v>
       </c>
-      <c r="E26" s="184" t="s">
+      <c r="E26" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F26" s="185">
+      <c r="F26" s="96">
         <v>6</v>
       </c>
-      <c r="G26" s="185">
+      <c r="G26" s="96">
         <v>0</v>
       </c>
-      <c r="H26" s="185">
+      <c r="H26" s="96">
         <v>8</v>
       </c>
-      <c r="I26" s="185">
+      <c r="I26" s="96">
         <v>14</v>
       </c>
-      <c r="J26" s="185">
+      <c r="J26" s="96">
         <v>14</v>
       </c>
-      <c r="K26" s="184" t="s">
+      <c r="K26" s="95" t="s">
         <v>967</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="120" x14ac:dyDescent="0.2">
-      <c r="A27" s="185">
+      <c r="A27" s="96">
         <v>55</v>
       </c>
-      <c r="B27" s="184" t="s">
+      <c r="B27" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="C27" s="184" t="s">
+      <c r="C27" s="95" t="s">
         <v>852</v>
       </c>
-      <c r="D27" s="184" t="s">
+      <c r="D27" s="95" t="s">
         <v>968</v>
       </c>
-      <c r="E27" s="184" t="s">
+      <c r="E27" s="95" t="s">
         <v>847</v>
       </c>
-      <c r="F27" s="185">
+      <c r="F27" s="96">
         <v>6</v>
       </c>
-      <c r="G27" s="185">
+      <c r="G27" s="96">
         <v>2</v>
       </c>
-      <c r="H27" s="185">
+      <c r="H27" s="96">
         <v>6</v>
       </c>
-      <c r="I27" s="185">
+      <c r="I27" s="96">
         <v>14</v>
       </c>
-      <c r="J27" s="185">
+      <c r="J27" s="96">
         <v>14</v>
       </c>
-      <c r="K27" s="184" t="s">
+      <c r="K27" s="95" t="s">
         <v>969</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="75" x14ac:dyDescent="0.2">
-      <c r="A28" s="185">
+      <c r="A28" s="96">
         <v>56</v>
       </c>
-      <c r="B28" s="184" t="s">
+      <c r="B28" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="C28" s="184" t="s">
+      <c r="C28" s="95" t="s">
         <v>856</v>
       </c>
-      <c r="D28" s="184" t="s">
+      <c r="D28" s="95" t="s">
         <v>970</v>
       </c>
-      <c r="E28" s="184" t="s">
+      <c r="E28" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F28" s="185">
+      <c r="F28" s="96">
         <v>9</v>
       </c>
-      <c r="G28" s="185">
+      <c r="G28" s="96">
         <v>0</v>
       </c>
-      <c r="H28" s="185">
+      <c r="H28" s="96">
         <v>5</v>
       </c>
-      <c r="I28" s="185">
+      <c r="I28" s="96">
         <v>14</v>
       </c>
-      <c r="J28" s="185">
+      <c r="J28" s="96">
         <v>14</v>
       </c>
-      <c r="K28" s="184" t="s">
+      <c r="K28" s="95" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="120" x14ac:dyDescent="0.2">
-      <c r="A29" s="185">
+      <c r="A29" s="96">
         <v>57</v>
       </c>
-      <c r="B29" s="184" t="s">
+      <c r="B29" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="C29" s="184" t="s">
+      <c r="C29" s="95" t="s">
         <v>857</v>
       </c>
-      <c r="D29" s="184" t="s">
+      <c r="D29" s="95" t="s">
         <v>972</v>
       </c>
-      <c r="E29" s="184" t="s">
+      <c r="E29" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F29" s="185">
+      <c r="F29" s="96">
         <v>6</v>
       </c>
-      <c r="G29" s="185">
+      <c r="G29" s="96">
         <v>0</v>
       </c>
-      <c r="H29" s="185">
+      <c r="H29" s="96">
         <v>8</v>
       </c>
-      <c r="I29" s="185">
+      <c r="I29" s="96">
         <v>14</v>
       </c>
-      <c r="J29" s="185">
+      <c r="J29" s="96">
         <v>14</v>
       </c>
-      <c r="K29" s="184" t="s">
+      <c r="K29" s="95" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="185">
+      <c r="A30" s="96">
         <v>2</v>
       </c>
-      <c r="B30" s="184" t="s">
+      <c r="B30" s="95" t="s">
         <v>900</v>
       </c>
-      <c r="C30" s="184" t="s">
+      <c r="C30" s="95" t="s">
         <v>331</v>
       </c>
-      <c r="D30" s="184" t="s">
+      <c r="D30" s="95" t="s">
         <v>511</v>
       </c>
-      <c r="E30" s="184" t="s">
+      <c r="E30" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F30" s="185">
+      <c r="F30" s="96">
         <v>5</v>
       </c>
-      <c r="G30" s="185">
+      <c r="G30" s="96">
         <v>8</v>
       </c>
-      <c r="H30" s="185">
+      <c r="H30" s="96">
         <v>0</v>
       </c>
-      <c r="I30" s="185">
+      <c r="I30" s="96">
         <v>13</v>
       </c>
-      <c r="J30" s="185">
+      <c r="J30" s="96">
         <v>13</v>
       </c>
-      <c r="K30" s="184" t="s">
+      <c r="K30" s="95" t="s">
         <v>901</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="185">
+      <c r="A31" s="96">
         <v>33</v>
       </c>
-      <c r="B31" s="184" t="s">
+      <c r="B31" s="95" t="s">
         <v>845</v>
       </c>
-      <c r="C31" s="184" t="s">
+      <c r="C31" s="95" t="s">
         <v>882</v>
       </c>
-      <c r="D31" s="184" t="s">
+      <c r="D31" s="95" t="s">
         <v>883</v>
       </c>
-      <c r="E31" s="184" t="s">
+      <c r="E31" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F31" s="185">
+      <c r="F31" s="96">
         <v>3</v>
       </c>
-      <c r="G31" s="185">
+      <c r="G31" s="96">
         <v>10</v>
       </c>
-      <c r="H31" s="185">
+      <c r="H31" s="96">
         <v>0</v>
       </c>
-      <c r="I31" s="185">
+      <c r="I31" s="96">
         <v>13</v>
       </c>
-      <c r="J31" s="185">
+      <c r="J31" s="96">
         <v>13</v>
       </c>
-      <c r="K31" s="184" t="s">
+      <c r="K31" s="95" t="s">
         <v>938</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="185">
+      <c r="A32" s="96">
         <v>34</v>
       </c>
-      <c r="B32" s="184" t="s">
+      <c r="B32" s="95" t="s">
         <v>845</v>
       </c>
-      <c r="C32" s="184" t="s">
+      <c r="C32" s="95" t="s">
         <v>888</v>
       </c>
-      <c r="D32" s="184" t="s">
+      <c r="D32" s="95" t="s">
         <v>889</v>
       </c>
-      <c r="E32" s="184" t="s">
+      <c r="E32" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F32" s="185">
+      <c r="F32" s="96">
         <v>3</v>
       </c>
-      <c r="G32" s="185">
+      <c r="G32" s="96">
         <v>10</v>
       </c>
-      <c r="H32" s="185">
+      <c r="H32" s="96">
         <v>0</v>
       </c>
-      <c r="I32" s="185">
+      <c r="I32" s="96">
         <v>13</v>
       </c>
-      <c r="J32" s="185">
+      <c r="J32" s="96">
         <v>13</v>
       </c>
-      <c r="K32" s="184" t="s">
+      <c r="K32" s="95" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="185">
+      <c r="A33" s="96">
         <v>36</v>
       </c>
-      <c r="B33" s="184" t="s">
+      <c r="B33" s="95" t="s">
         <v>182</v>
       </c>
-      <c r="C33" s="184" t="s">
+      <c r="C33" s="95" t="s">
         <v>514</v>
       </c>
-      <c r="D33" s="184" t="s">
+      <c r="D33" s="95" t="s">
         <v>513</v>
       </c>
-      <c r="E33" s="184" t="s">
+      <c r="E33" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F33" s="185">
+      <c r="F33" s="96">
         <v>3</v>
       </c>
-      <c r="G33" s="185">
+      <c r="G33" s="96">
         <v>10</v>
       </c>
-      <c r="H33" s="185">
+      <c r="H33" s="96">
         <v>0</v>
       </c>
-      <c r="I33" s="185">
+      <c r="I33" s="96">
         <v>13</v>
       </c>
-      <c r="J33" s="185">
+      <c r="J33" s="96">
         <v>13</v>
       </c>
-      <c r="K33" s="184" t="s">
+      <c r="K33" s="95" t="s">
         <v>941</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="120" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="185">
+      <c r="A34" s="96">
         <v>37</v>
       </c>
-      <c r="B34" s="184" t="s">
+      <c r="B34" s="95" t="s">
         <v>182</v>
       </c>
-      <c r="C34" s="184" t="s">
+      <c r="C34" s="95" t="s">
         <v>199</v>
       </c>
-      <c r="D34" s="184" t="s">
+      <c r="D34" s="95" t="s">
         <v>437</v>
       </c>
-      <c r="E34" s="184" t="s">
+      <c r="E34" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F34" s="185">
+      <c r="F34" s="96">
         <v>3</v>
       </c>
-      <c r="G34" s="185">
+      <c r="G34" s="96">
         <v>10</v>
       </c>
-      <c r="H34" s="185">
+      <c r="H34" s="96">
         <v>0</v>
       </c>
-      <c r="I34" s="185">
+      <c r="I34" s="96">
         <v>13</v>
       </c>
-      <c r="J34" s="185">
+      <c r="J34" s="96">
         <v>13</v>
       </c>
-      <c r="K34" s="184" t="s">
+      <c r="K34" s="95" t="s">
         <v>942</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="185">
+      <c r="A35" s="96">
         <v>66</v>
       </c>
-      <c r="B35" s="184" t="s">
+      <c r="B35" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C35" s="184" t="s">
+      <c r="C35" s="95" t="s">
         <v>831</v>
       </c>
-      <c r="D35" s="184" t="s">
+      <c r="D35" s="95" t="s">
         <v>983</v>
       </c>
-      <c r="E35" s="184" t="s">
+      <c r="E35" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F35" s="185">
+      <c r="F35" s="96">
         <v>3</v>
       </c>
-      <c r="G35" s="185">
+      <c r="G35" s="96">
         <v>10</v>
       </c>
-      <c r="H35" s="185">
+      <c r="H35" s="96">
         <v>0</v>
       </c>
-      <c r="I35" s="185">
+      <c r="I35" s="96">
         <v>13</v>
       </c>
-      <c r="J35" s="185">
+      <c r="J35" s="96">
         <v>13</v>
       </c>
-      <c r="K35" s="184" t="s">
+      <c r="K35" s="95" t="s">
         <v>984</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="185">
+      <c r="A36" s="96">
         <v>67</v>
       </c>
-      <c r="B36" s="184" t="s">
+      <c r="B36" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C36" s="184" t="s">
+      <c r="C36" s="95" t="s">
         <v>833</v>
       </c>
-      <c r="D36" s="184" t="s">
+      <c r="D36" s="95" t="s">
         <v>985</v>
       </c>
-      <c r="E36" s="184" t="s">
+      <c r="E36" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F36" s="185">
+      <c r="F36" s="96">
         <v>3</v>
       </c>
-      <c r="G36" s="185">
+      <c r="G36" s="96">
         <v>10</v>
       </c>
-      <c r="H36" s="185">
+      <c r="H36" s="96">
         <v>0</v>
       </c>
-      <c r="I36" s="185">
+      <c r="I36" s="96">
         <v>13</v>
       </c>
-      <c r="J36" s="185">
+      <c r="J36" s="96">
         <v>13</v>
       </c>
-      <c r="K36" s="184" t="s">
+      <c r="K36" s="95" t="s">
         <v>986</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="185">
+      <c r="A37" s="96">
         <v>68</v>
       </c>
-      <c r="B37" s="184" t="s">
+      <c r="B37" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C37" s="184" t="s">
+      <c r="C37" s="95" t="s">
         <v>840</v>
       </c>
-      <c r="D37" s="184" t="s">
+      <c r="D37" s="95" t="s">
         <v>987</v>
       </c>
-      <c r="E37" s="184" t="s">
+      <c r="E37" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F37" s="185">
+      <c r="F37" s="96">
         <v>3</v>
       </c>
-      <c r="G37" s="185">
+      <c r="G37" s="96">
         <v>10</v>
       </c>
-      <c r="H37" s="185">
+      <c r="H37" s="96">
         <v>0</v>
       </c>
-      <c r="I37" s="185">
+      <c r="I37" s="96">
         <v>13</v>
       </c>
-      <c r="J37" s="185">
+      <c r="J37" s="96">
         <v>13</v>
       </c>
-      <c r="K37" s="184" t="s">
+      <c r="K37" s="95" t="s">
         <v>988</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="185">
+      <c r="A38" s="96">
         <v>69</v>
       </c>
-      <c r="B38" s="184" t="s">
+      <c r="B38" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C38" s="184" t="s">
+      <c r="C38" s="95" t="s">
         <v>841</v>
       </c>
-      <c r="D38" s="184" t="s">
+      <c r="D38" s="95" t="s">
         <v>989</v>
       </c>
-      <c r="E38" s="184" t="s">
+      <c r="E38" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F38" s="185">
+      <c r="F38" s="96">
         <v>3</v>
       </c>
-      <c r="G38" s="185">
+      <c r="G38" s="96">
         <v>10</v>
       </c>
-      <c r="H38" s="185">
+      <c r="H38" s="96">
         <v>0</v>
       </c>
-      <c r="I38" s="185">
+      <c r="I38" s="96">
         <v>13</v>
       </c>
-      <c r="J38" s="185">
+      <c r="J38" s="96">
         <v>13</v>
       </c>
-      <c r="K38" s="184" t="s">
+      <c r="K38" s="95" t="s">
         <v>990</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="185">
+      <c r="A39" s="96">
         <v>71</v>
       </c>
-      <c r="B39" s="184" t="s">
+      <c r="B39" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C39" s="184" t="s">
+      <c r="C39" s="95" t="s">
         <v>853</v>
       </c>
-      <c r="D39" s="184" t="s">
+      <c r="D39" s="95" t="s">
         <v>994</v>
       </c>
-      <c r="E39" s="184" t="s">
+      <c r="E39" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F39" s="185">
+      <c r="F39" s="96">
         <v>1</v>
       </c>
-      <c r="G39" s="185">
+      <c r="G39" s="96">
         <v>12</v>
       </c>
-      <c r="H39" s="185">
+      <c r="H39" s="96">
         <v>0</v>
       </c>
-      <c r="I39" s="185">
+      <c r="I39" s="96">
         <v>13</v>
       </c>
-      <c r="J39" s="185">
+      <c r="J39" s="96">
         <v>13</v>
       </c>
-      <c r="K39" s="184" t="s">
+      <c r="K39" s="95" t="s">
         <v>995</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="120" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="185">
+      <c r="A40" s="96">
         <v>74</v>
       </c>
-      <c r="B40" s="184" t="s">
+      <c r="B40" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C40" s="184" t="s">
+      <c r="C40" s="95" t="s">
         <v>586</v>
       </c>
-      <c r="D40" s="184" t="s">
+      <c r="D40" s="95" t="s">
         <v>585</v>
       </c>
-      <c r="E40" s="184" t="s">
+      <c r="E40" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F40" s="185">
+      <c r="F40" s="96">
         <v>3</v>
       </c>
-      <c r="G40" s="185">
+      <c r="G40" s="96">
         <v>10</v>
       </c>
-      <c r="H40" s="185">
+      <c r="H40" s="96">
         <v>0</v>
       </c>
-      <c r="I40" s="185">
+      <c r="I40" s="96">
         <v>13</v>
       </c>
-      <c r="J40" s="185">
+      <c r="J40" s="96">
         <v>13</v>
       </c>
-      <c r="K40" s="184" t="s">
+      <c r="K40" s="95" t="s">
         <v>1000</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="185">
+      <c r="A41" s="96">
         <v>75</v>
       </c>
-      <c r="B41" s="184" t="s">
+      <c r="B41" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C41" s="184" t="s">
+      <c r="C41" s="95" t="s">
         <v>863</v>
       </c>
-      <c r="D41" s="184" t="s">
+      <c r="D41" s="95" t="s">
         <v>864</v>
       </c>
-      <c r="E41" s="184" t="s">
+      <c r="E41" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F41" s="185">
+      <c r="F41" s="96">
         <v>3</v>
       </c>
-      <c r="G41" s="185">
+      <c r="G41" s="96">
         <v>10</v>
       </c>
-      <c r="H41" s="185">
+      <c r="H41" s="96">
         <v>0</v>
       </c>
-      <c r="I41" s="185">
+      <c r="I41" s="96">
         <v>13</v>
       </c>
-      <c r="J41" s="185">
+      <c r="J41" s="96">
         <v>13</v>
       </c>
-      <c r="K41" s="184" t="s">
+      <c r="K41" s="95" t="s">
         <v>1001</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="185">
+      <c r="A42" s="96">
         <v>76</v>
       </c>
-      <c r="B42" s="184" t="s">
+      <c r="B42" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C42" s="184" t="s">
+      <c r="C42" s="95" t="s">
         <v>867</v>
       </c>
-      <c r="D42" s="184" t="s">
+      <c r="D42" s="95" t="s">
         <v>868</v>
       </c>
-      <c r="E42" s="184" t="s">
+      <c r="E42" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F42" s="185">
+      <c r="F42" s="96">
         <v>1</v>
       </c>
-      <c r="G42" s="185">
+      <c r="G42" s="96">
         <v>12</v>
       </c>
-      <c r="H42" s="185">
+      <c r="H42" s="96">
         <v>0</v>
       </c>
-      <c r="I42" s="185">
+      <c r="I42" s="96">
         <v>13</v>
       </c>
-      <c r="J42" s="185">
+      <c r="J42" s="96">
         <v>13</v>
       </c>
-      <c r="K42" s="184" t="s">
+      <c r="K42" s="95" t="s">
         <v>1002</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="185">
+      <c r="A43" s="96">
         <v>77</v>
       </c>
-      <c r="B43" s="184" t="s">
+      <c r="B43" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C43" s="184" t="s">
+      <c r="C43" s="95" t="s">
         <v>873</v>
       </c>
-      <c r="D43" s="184" t="s">
+      <c r="D43" s="95" t="s">
         <v>874</v>
       </c>
-      <c r="E43" s="184" t="s">
+      <c r="E43" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F43" s="185">
+      <c r="F43" s="96">
         <v>3</v>
       </c>
-      <c r="G43" s="185">
+      <c r="G43" s="96">
         <v>10</v>
       </c>
-      <c r="H43" s="185">
+      <c r="H43" s="96">
         <v>0</v>
       </c>
-      <c r="I43" s="185">
+      <c r="I43" s="96">
         <v>13</v>
       </c>
-      <c r="J43" s="185">
+      <c r="J43" s="96">
         <v>13</v>
       </c>
-      <c r="K43" s="184" t="s">
+      <c r="K43" s="95" t="s">
         <v>1003</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="185">
+      <c r="A44" s="96">
         <v>15</v>
       </c>
-      <c r="B44" s="184" t="s">
+      <c r="B44" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="184" t="s">
+      <c r="C44" s="95" t="s">
         <v>877</v>
       </c>
-      <c r="D44" s="184" t="s">
+      <c r="D44" s="95" t="s">
         <v>878</v>
       </c>
-      <c r="E44" s="184" t="s">
+      <c r="E44" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F44" s="185">
+      <c r="F44" s="96">
         <v>8</v>
       </c>
-      <c r="G44" s="185">
+      <c r="G44" s="96">
         <v>4</v>
       </c>
-      <c r="H44" s="185">
+      <c r="H44" s="96">
         <v>0</v>
       </c>
-      <c r="I44" s="185">
+      <c r="I44" s="96">
         <v>12</v>
       </c>
-      <c r="J44" s="185">
+      <c r="J44" s="96">
         <v>12</v>
       </c>
-      <c r="K44" s="184" t="s">
+      <c r="K44" s="95" t="s">
         <v>917</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="185">
+      <c r="A45" s="96">
         <v>28</v>
       </c>
-      <c r="B45" s="184" t="s">
+      <c r="B45" s="95" t="s">
         <v>845</v>
       </c>
-      <c r="C45" s="184" t="s">
+      <c r="C45" s="95" t="s">
         <v>253</v>
       </c>
-      <c r="D45" s="184" t="s">
+      <c r="D45" s="95" t="s">
         <v>622</v>
       </c>
-      <c r="E45" s="184" t="s">
+      <c r="E45" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="F45" s="185">
+      <c r="F45" s="96">
         <v>4</v>
       </c>
-      <c r="G45" s="185">
+      <c r="G45" s="96">
         <v>8</v>
       </c>
-      <c r="H45" s="185">
+      <c r="H45" s="96">
         <v>0</v>
       </c>
-      <c r="I45" s="185">
+      <c r="I45" s="96">
         <v>12</v>
       </c>
-      <c r="J45" s="185">
+      <c r="J45" s="96">
         <v>12</v>
       </c>
-      <c r="K45" s="184" t="s">
+      <c r="K45" s="95" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="185">
+      <c r="A46" s="96">
         <v>38</v>
       </c>
-      <c r="B46" s="184" t="s">
+      <c r="B46" s="95" t="s">
         <v>826</v>
       </c>
-      <c r="C46" s="184" t="s">
+      <c r="C46" s="95" t="s">
         <v>519</v>
       </c>
-      <c r="D46" s="184" t="s">
+      <c r="D46" s="95" t="s">
         <v>518</v>
       </c>
-      <c r="E46" s="184" t="s">
+      <c r="E46" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F46" s="185">
+      <c r="F46" s="96">
         <v>0</v>
       </c>
-      <c r="G46" s="185">
+      <c r="G46" s="96">
         <v>10</v>
       </c>
-      <c r="H46" s="185">
+      <c r="H46" s="96">
         <v>2</v>
       </c>
-      <c r="I46" s="185">
+      <c r="I46" s="96">
         <v>12</v>
       </c>
-      <c r="J46" s="185">
+      <c r="J46" s="96">
         <v>12</v>
       </c>
-      <c r="K46" s="184" t="s">
+      <c r="K46" s="95" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="185">
+      <c r="A47" s="96">
         <v>39</v>
       </c>
-      <c r="B47" s="184" t="s">
+      <c r="B47" s="95" t="s">
         <v>826</v>
       </c>
-      <c r="C47" s="184" t="s">
+      <c r="C47" s="95" t="s">
         <v>632</v>
       </c>
-      <c r="D47" s="184" t="s">
+      <c r="D47" s="95" t="s">
         <v>631</v>
       </c>
-      <c r="E47" s="184" t="s">
+      <c r="E47" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F47" s="185">
+      <c r="F47" s="96">
         <v>0</v>
       </c>
-      <c r="G47" s="185">
+      <c r="G47" s="96">
         <v>10</v>
       </c>
-      <c r="H47" s="185">
+      <c r="H47" s="96">
         <v>2</v>
       </c>
-      <c r="I47" s="185">
+      <c r="I47" s="96">
         <v>12</v>
       </c>
-      <c r="J47" s="185">
+      <c r="J47" s="96">
         <v>12</v>
       </c>
-      <c r="K47" s="184" t="s">
+      <c r="K47" s="95" t="s">
         <v>944</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="185">
+      <c r="A48" s="96">
         <v>40</v>
       </c>
-      <c r="B48" s="184" t="s">
+      <c r="B48" s="95" t="s">
         <v>826</v>
       </c>
-      <c r="C48" s="184" t="s">
+      <c r="C48" s="95" t="s">
         <v>846</v>
       </c>
-      <c r="D48" s="184" t="s">
+      <c r="D48" s="95" t="s">
         <v>945</v>
       </c>
-      <c r="E48" s="184" t="s">
+      <c r="E48" s="95" t="s">
         <v>847</v>
       </c>
-      <c r="F48" s="185">
+      <c r="F48" s="96">
         <v>0</v>
       </c>
-      <c r="G48" s="185">
+      <c r="G48" s="96">
         <v>10</v>
       </c>
-      <c r="H48" s="185">
+      <c r="H48" s="96">
         <v>2</v>
       </c>
-      <c r="I48" s="185">
+      <c r="I48" s="96">
         <v>12</v>
       </c>
-      <c r="J48" s="185">
+      <c r="J48" s="96">
         <v>12</v>
       </c>
-      <c r="K48" s="184" t="s">
+      <c r="K48" s="95" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="185">
+      <c r="A49" s="96">
         <v>43</v>
       </c>
-      <c r="B49" s="184" t="s">
+      <c r="B49" s="95" t="s">
         <v>826</v>
       </c>
-      <c r="C49" s="184" t="s">
+      <c r="C49" s="95" t="s">
         <v>447</v>
       </c>
-      <c r="D49" s="184" t="s">
+      <c r="D49" s="95" t="s">
         <v>446</v>
       </c>
-      <c r="E49" s="184" t="s">
+      <c r="E49" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F49" s="185">
+      <c r="F49" s="96">
         <v>0</v>
       </c>
-      <c r="G49" s="185">
+      <c r="G49" s="96">
         <v>10</v>
       </c>
-      <c r="H49" s="185">
+      <c r="H49" s="96">
         <v>2</v>
       </c>
-      <c r="I49" s="185">
+      <c r="I49" s="96">
         <v>12</v>
       </c>
-      <c r="J49" s="185">
+      <c r="J49" s="96">
         <v>12</v>
       </c>
-      <c r="K49" s="184" t="s">
+      <c r="K49" s="95" t="s">
         <v>950</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="185">
+      <c r="A50" s="96">
         <v>47</v>
       </c>
-      <c r="B50" s="184" t="s">
+      <c r="B50" s="95" t="s">
         <v>851</v>
       </c>
-      <c r="C50" s="184" t="s">
+      <c r="C50" s="95" t="s">
         <v>869</v>
       </c>
-      <c r="D50" s="184" t="s">
+      <c r="D50" s="95" t="s">
         <v>870</v>
       </c>
-      <c r="E50" s="184" t="s">
+      <c r="E50" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F50" s="185">
+      <c r="F50" s="96">
         <v>6</v>
       </c>
-      <c r="G50" s="185">
+      <c r="G50" s="96">
         <v>6</v>
       </c>
-      <c r="H50" s="185">
+      <c r="H50" s="96">
         <v>0</v>
       </c>
-      <c r="I50" s="185">
+      <c r="I50" s="96">
         <v>12</v>
       </c>
-      <c r="J50" s="185">
+      <c r="J50" s="96">
         <v>12</v>
       </c>
-      <c r="K50" s="184" t="s">
+      <c r="K50" s="95" t="s">
         <v>957</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="185">
+      <c r="A51" s="96">
         <v>59</v>
       </c>
-      <c r="B51" s="184" t="s">
+      <c r="B51" s="95" t="s">
         <v>830</v>
       </c>
-      <c r="C51" s="184" t="s">
+      <c r="C51" s="95" t="s">
         <v>256</v>
       </c>
-      <c r="D51" s="184" t="s">
+      <c r="D51" s="95" t="s">
         <v>976</v>
       </c>
-      <c r="E51" s="184" t="s">
+      <c r="E51" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="F51" s="185">
+      <c r="F51" s="96">
         <v>4</v>
       </c>
-      <c r="G51" s="185">
+      <c r="G51" s="96">
         <v>8</v>
       </c>
-      <c r="H51" s="185">
+      <c r="H51" s="96">
         <v>0</v>
       </c>
-      <c r="I51" s="185">
+      <c r="I51" s="96">
         <v>12</v>
       </c>
-      <c r="J51" s="185">
+      <c r="J51" s="96">
         <v>12</v>
       </c>
-      <c r="K51" s="184" t="s">
+      <c r="K51" s="95" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="185">
+      <c r="A52" s="96">
         <v>61</v>
       </c>
-      <c r="B52" s="184" t="s">
+      <c r="B52" s="95" t="s">
         <v>830</v>
       </c>
-      <c r="C52" s="184" t="s">
+      <c r="C52" s="95" t="s">
         <v>875</v>
       </c>
-      <c r="D52" s="184" t="s">
+      <c r="D52" s="95" t="s">
         <v>876</v>
       </c>
-      <c r="E52" s="184" t="s">
+      <c r="E52" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F52" s="185">
+      <c r="F52" s="96">
         <v>0</v>
       </c>
-      <c r="G52" s="185">
+      <c r="G52" s="96">
         <v>12</v>
       </c>
-      <c r="H52" s="185">
+      <c r="H52" s="96">
         <v>0</v>
       </c>
-      <c r="I52" s="185">
+      <c r="I52" s="96">
         <v>12</v>
       </c>
-      <c r="J52" s="185">
+      <c r="J52" s="96">
         <v>12</v>
       </c>
-      <c r="K52" s="184" t="s">
+      <c r="K52" s="95" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="185">
+      <c r="A53" s="96">
         <v>63</v>
       </c>
-      <c r="B53" s="184" t="s">
+      <c r="B53" s="95" t="s">
         <v>830</v>
       </c>
-      <c r="C53" s="184" t="s">
+      <c r="C53" s="95" t="s">
         <v>886</v>
       </c>
-      <c r="D53" s="184" t="s">
+      <c r="D53" s="95" t="s">
         <v>887</v>
       </c>
-      <c r="E53" s="184" t="s">
+      <c r="E53" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F53" s="185">
+      <c r="F53" s="96">
         <v>2</v>
       </c>
-      <c r="G53" s="185">
+      <c r="G53" s="96">
         <v>10</v>
       </c>
-      <c r="H53" s="185">
+      <c r="H53" s="96">
         <v>0</v>
       </c>
-      <c r="I53" s="185">
+      <c r="I53" s="96">
         <v>12</v>
       </c>
-      <c r="J53" s="185">
+      <c r="J53" s="96">
         <v>12</v>
       </c>
-      <c r="K53" s="184" t="s">
+      <c r="K53" s="95" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="185">
+      <c r="A54" s="96">
         <v>64</v>
       </c>
-      <c r="B54" s="184" t="s">
+      <c r="B54" s="95" t="s">
         <v>830</v>
       </c>
-      <c r="C54" s="184" t="s">
+      <c r="C54" s="95" t="s">
         <v>890</v>
       </c>
-      <c r="D54" s="184" t="s">
+      <c r="D54" s="95" t="s">
         <v>891</v>
       </c>
-      <c r="E54" s="184" t="s">
+      <c r="E54" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F54" s="185">
+      <c r="F54" s="96">
         <v>2</v>
       </c>
-      <c r="G54" s="185">
+      <c r="G54" s="96">
         <v>10</v>
       </c>
-      <c r="H54" s="185">
+      <c r="H54" s="96">
         <v>0</v>
       </c>
-      <c r="I54" s="185">
+      <c r="I54" s="96">
         <v>12</v>
       </c>
-      <c r="J54" s="185">
+      <c r="J54" s="96">
         <v>12</v>
       </c>
-      <c r="K54" s="184" t="s">
+      <c r="K54" s="95" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="185">
+      <c r="A55" s="96">
         <v>70</v>
       </c>
-      <c r="B55" s="184" t="s">
+      <c r="B55" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C55" s="184" t="s">
+      <c r="C55" s="95" t="s">
         <v>320</v>
       </c>
-      <c r="D55" s="184" t="s">
+      <c r="D55" s="95" t="s">
         <v>991</v>
       </c>
-      <c r="E55" s="184" t="s">
+      <c r="E55" s="95" t="s">
         <v>992</v>
       </c>
-      <c r="F55" s="185">
+      <c r="F55" s="96">
         <v>4</v>
       </c>
-      <c r="G55" s="185">
+      <c r="G55" s="96">
         <v>8</v>
       </c>
-      <c r="H55" s="185">
+      <c r="H55" s="96">
         <v>0</v>
       </c>
-      <c r="I55" s="185">
+      <c r="I55" s="96">
         <v>12</v>
       </c>
-      <c r="J55" s="185">
+      <c r="J55" s="96">
         <v>12</v>
       </c>
-      <c r="K55" s="184" t="s">
+      <c r="K55" s="95" t="s">
         <v>993</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="185">
+      <c r="A56" s="96">
         <v>16</v>
       </c>
-      <c r="B56" s="184" t="s">
+      <c r="B56" s="95" t="s">
         <v>836</v>
       </c>
-      <c r="C56" s="184" t="s">
+      <c r="C56" s="95" t="s">
         <v>835</v>
       </c>
-      <c r="D56" s="184" t="s">
+      <c r="D56" s="95" t="s">
         <v>918</v>
       </c>
-      <c r="E56" s="184" t="s">
+      <c r="E56" s="95" t="s">
         <v>837</v>
       </c>
-      <c r="F56" s="185">
+      <c r="F56" s="96">
         <v>3</v>
       </c>
-      <c r="G56" s="185">
+      <c r="G56" s="96">
         <v>8</v>
       </c>
-      <c r="H56" s="185">
+      <c r="H56" s="96">
         <v>0</v>
       </c>
-      <c r="I56" s="185">
+      <c r="I56" s="96">
         <v>11</v>
       </c>
-      <c r="J56" s="185">
+      <c r="J56" s="96">
         <v>11</v>
       </c>
-      <c r="K56" s="184" t="s">
+      <c r="K56" s="95" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="185">
+      <c r="A57" s="96">
         <v>30</v>
       </c>
-      <c r="B57" s="184" t="s">
+      <c r="B57" s="95" t="s">
         <v>845</v>
       </c>
-      <c r="C57" s="184" t="s">
+      <c r="C57" s="95" t="s">
         <v>202</v>
       </c>
-      <c r="D57" s="184" t="s">
+      <c r="D57" s="95" t="s">
         <v>440</v>
       </c>
-      <c r="E57" s="184" t="s">
+      <c r="E57" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F57" s="185">
+      <c r="F57" s="96">
         <v>3</v>
       </c>
-      <c r="G57" s="185">
+      <c r="G57" s="96">
         <v>8</v>
       </c>
-      <c r="H57" s="185">
+      <c r="H57" s="96">
         <v>0</v>
       </c>
-      <c r="I57" s="185">
+      <c r="I57" s="96">
         <v>11</v>
       </c>
-      <c r="J57" s="185">
+      <c r="J57" s="96">
         <v>11</v>
       </c>
-      <c r="K57" s="184" t="s">
+      <c r="K57" s="95" t="s">
         <v>935</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="185">
+      <c r="A58" s="96">
         <v>31</v>
       </c>
-      <c r="B58" s="184" t="s">
+      <c r="B58" s="95" t="s">
         <v>845</v>
       </c>
-      <c r="C58" s="184" t="s">
+      <c r="C58" s="95" t="s">
         <v>879</v>
       </c>
-      <c r="D58" s="184" t="s">
+      <c r="D58" s="95" t="s">
         <v>880</v>
       </c>
-      <c r="E58" s="184" t="s">
+      <c r="E58" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F58" s="185">
+      <c r="F58" s="96">
         <v>3</v>
       </c>
-      <c r="G58" s="185">
+      <c r="G58" s="96">
         <v>8</v>
       </c>
-      <c r="H58" s="185">
+      <c r="H58" s="96">
         <v>0</v>
       </c>
-      <c r="I58" s="185">
+      <c r="I58" s="96">
         <v>11</v>
       </c>
-      <c r="J58" s="185">
+      <c r="J58" s="96">
         <v>11</v>
       </c>
-      <c r="K58" s="184" t="s">
+      <c r="K58" s="95" t="s">
         <v>936</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="185">
+      <c r="A59" s="96">
         <v>35</v>
       </c>
-      <c r="B59" s="184" t="s">
+      <c r="B59" s="95" t="s">
         <v>182</v>
       </c>
-      <c r="C59" s="184" t="s">
+      <c r="C59" s="95" t="s">
         <v>865</v>
       </c>
-      <c r="D59" s="184" t="s">
+      <c r="D59" s="95" t="s">
         <v>866</v>
       </c>
-      <c r="E59" s="184" t="s">
+      <c r="E59" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="F59" s="185">
+      <c r="F59" s="96">
         <v>1</v>
       </c>
-      <c r="G59" s="185">
+      <c r="G59" s="96">
         <v>10</v>
       </c>
-      <c r="H59" s="185">
+      <c r="H59" s="96">
         <v>0</v>
       </c>
-      <c r="I59" s="185">
+      <c r="I59" s="96">
         <v>11</v>
       </c>
-      <c r="J59" s="185">
+      <c r="J59" s="96">
         <v>11</v>
       </c>
-      <c r="K59" s="184" t="s">
+      <c r="K59" s="95" t="s">
         <v>940</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="185">
+      <c r="A60" s="96">
         <v>42</v>
       </c>
-      <c r="B60" s="184" t="s">
+      <c r="B60" s="95" t="s">
         <v>826</v>
       </c>
-      <c r="C60" s="184" t="s">
+      <c r="C60" s="95" t="s">
         <v>337</v>
       </c>
-      <c r="D60" s="184" t="s">
+      <c r="D60" s="95" t="s">
         <v>555</v>
       </c>
-      <c r="E60" s="184" t="s">
+      <c r="E60" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F60" s="185">
+      <c r="F60" s="96">
         <v>0</v>
       </c>
-      <c r="G60" s="185">
+      <c r="G60" s="96">
         <v>10</v>
       </c>
-      <c r="H60" s="185">
+      <c r="H60" s="96">
         <v>1</v>
       </c>
-      <c r="I60" s="185">
+      <c r="I60" s="96">
         <v>11</v>
       </c>
-      <c r="J60" s="185">
+      <c r="J60" s="96">
         <v>11</v>
       </c>
-      <c r="K60" s="184" t="s">
+      <c r="K60" s="95" t="s">
         <v>949</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="90" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="185">
+      <c r="A61" s="96">
         <v>44</v>
       </c>
-      <c r="B61" s="184" t="s">
+      <c r="B61" s="95" t="s">
         <v>826</v>
       </c>
-      <c r="C61" s="184" t="s">
+      <c r="C61" s="95" t="s">
         <v>593</v>
       </c>
-      <c r="D61" s="184" t="s">
+      <c r="D61" s="95" t="s">
         <v>591</v>
       </c>
-      <c r="E61" s="184" t="s">
+      <c r="E61" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F61" s="185">
+      <c r="F61" s="96">
         <v>0</v>
       </c>
-      <c r="G61" s="185">
+      <c r="G61" s="96">
         <v>10</v>
       </c>
-      <c r="H61" s="185">
+      <c r="H61" s="96">
         <v>1</v>
       </c>
-      <c r="I61" s="185">
+      <c r="I61" s="96">
         <v>11</v>
       </c>
-      <c r="J61" s="185">
+      <c r="J61" s="96">
         <v>11</v>
       </c>
-      <c r="K61" s="184" t="s">
+      <c r="K61" s="95" t="s">
         <v>951</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="105" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="185">
+      <c r="A62" s="96">
         <v>45</v>
       </c>
-      <c r="B62" s="184" t="s">
+      <c r="B62" s="95" t="s">
         <v>851</v>
       </c>
-      <c r="C62" s="184" t="s">
+      <c r="C62" s="95" t="s">
         <v>850</v>
       </c>
-      <c r="D62" s="184" t="s">
+      <c r="D62" s="95" t="s">
         <v>952</v>
       </c>
-      <c r="E62" s="184" t="s">
+      <c r="E62" s="95" t="s">
         <v>837</v>
       </c>
-      <c r="F62" s="185">
+      <c r="F62" s="96">
         <v>3</v>
       </c>
-      <c r="G62" s="185">
+      <c r="G62" s="96">
         <v>8</v>
       </c>
-      <c r="H62" s="185">
+      <c r="H62" s="96">
         <v>0</v>
       </c>
-      <c r="I62" s="185">
+      <c r="I62" s="96">
         <v>11</v>
       </c>
-      <c r="J62" s="185">
+      <c r="J62" s="96">
         <v>11</v>
       </c>
-      <c r="K62" s="184" t="s">
+      <c r="K62" s="95" t="s">
         <v>953</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="185">
+      <c r="A63" s="96">
         <v>1</v>
       </c>
-      <c r="B63" s="184" t="s">
+      <c r="B63" s="95" t="s">
         <v>1004</v>
       </c>
-      <c r="C63" s="184" t="s">
+      <c r="C63" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D63" s="184" t="s">
+      <c r="D63" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="E63" s="184" t="s">
+      <c r="E63" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F63" s="185">
+      <c r="F63" s="96">
         <v>0</v>
       </c>
-      <c r="G63" s="185">
+      <c r="G63" s="96">
         <v>10</v>
       </c>
-      <c r="H63" s="185">
+      <c r="H63" s="96">
         <v>0</v>
       </c>
-      <c r="I63" s="185">
+      <c r="I63" s="96">
         <v>10</v>
       </c>
-      <c r="J63" s="185">
+      <c r="J63" s="96">
         <v>10</v>
       </c>
-      <c r="K63" s="184" t="s">
+      <c r="K63" s="95" t="s">
         <v>899</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="185">
+      <c r="A64" s="96">
         <v>10</v>
       </c>
-      <c r="B64" s="184" t="s">
+      <c r="B64" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="C64" s="184" t="s">
+      <c r="C64" s="95" t="s">
         <v>327</v>
       </c>
-      <c r="D64" s="184" t="s">
+      <c r="D64" s="95" t="s">
         <v>516</v>
       </c>
-      <c r="E64" s="184" t="s">
+      <c r="E64" s="95" t="s">
         <v>837</v>
       </c>
-      <c r="F64" s="185">
+      <c r="F64" s="96">
         <v>6</v>
       </c>
-      <c r="G64" s="185">
+      <c r="G64" s="96">
         <v>4</v>
       </c>
-      <c r="H64" s="185">
+      <c r="H64" s="96">
         <v>0</v>
       </c>
-      <c r="I64" s="185">
+      <c r="I64" s="96">
         <v>10</v>
       </c>
-      <c r="J64" s="185">
+      <c r="J64" s="96">
         <v>10</v>
       </c>
-      <c r="K64" s="184" t="s">
+      <c r="K64" s="95" t="s">
         <v>912</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="185">
+      <c r="A65" s="96">
         <v>11</v>
       </c>
-      <c r="B65" s="184" t="s">
+      <c r="B65" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="C65" s="184" t="s">
+      <c r="C65" s="95" t="s">
         <v>444</v>
       </c>
-      <c r="D65" s="184" t="s">
+      <c r="D65" s="95" t="s">
         <v>443</v>
       </c>
-      <c r="E65" s="184" t="s">
+      <c r="E65" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="F65" s="185">
+      <c r="F65" s="96">
         <v>8</v>
       </c>
-      <c r="G65" s="185">
+      <c r="G65" s="96">
         <v>2</v>
       </c>
-      <c r="H65" s="185">
+      <c r="H65" s="96">
         <v>0</v>
       </c>
-      <c r="I65" s="185">
+      <c r="I65" s="96">
         <v>10</v>
       </c>
-      <c r="J65" s="185">
+      <c r="J65" s="96">
         <v>10</v>
       </c>
-      <c r="K65" s="184" t="s">
+      <c r="K65" s="95" t="s">
         <v>913</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="185">
+      <c r="A66" s="96">
         <v>12</v>
       </c>
-      <c r="B66" s="184" t="s">
+      <c r="B66" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="C66" s="184" t="s">
+      <c r="C66" s="95" t="s">
         <v>313</v>
       </c>
-      <c r="D66" s="184" t="s">
+      <c r="D66" s="95" t="s">
         <v>553</v>
       </c>
-      <c r="E66" s="184" t="s">
+      <c r="E66" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F66" s="185">
+      <c r="F66" s="96">
         <v>8</v>
       </c>
-      <c r="G66" s="185">
+      <c r="G66" s="96">
         <v>2</v>
       </c>
-      <c r="H66" s="185">
+      <c r="H66" s="96">
         <v>0</v>
       </c>
-      <c r="I66" s="185">
+      <c r="I66" s="96">
         <v>10</v>
       </c>
-      <c r="J66" s="185">
+      <c r="J66" s="96">
         <v>10</v>
       </c>
-      <c r="K66" s="184" t="s">
+      <c r="K66" s="95" t="s">
         <v>914</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="185">
+      <c r="A67" s="96">
         <v>32</v>
       </c>
-      <c r="B67" s="184" t="s">
+      <c r="B67" s="95" t="s">
         <v>845</v>
       </c>
-      <c r="C67" s="184" t="s">
+      <c r="C67" s="95" t="s">
         <v>315</v>
       </c>
-      <c r="D67" s="184" t="s">
+      <c r="D67" s="95" t="s">
         <v>881</v>
       </c>
-      <c r="E67" s="184" t="s">
+      <c r="E67" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F67" s="185">
+      <c r="F67" s="96">
         <v>0</v>
       </c>
-      <c r="G67" s="185">
+      <c r="G67" s="96">
         <v>10</v>
       </c>
-      <c r="H67" s="185">
+      <c r="H67" s="96">
         <v>0</v>
       </c>
-      <c r="I67" s="185">
+      <c r="I67" s="96">
         <v>10</v>
       </c>
-      <c r="J67" s="185">
+      <c r="J67" s="96">
         <v>10</v>
       </c>
-      <c r="K67" s="184" t="s">
+      <c r="K67" s="95" t="s">
         <v>937</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="185">
+      <c r="A68" s="96">
         <v>46</v>
       </c>
-      <c r="B68" s="184" t="s">
+      <c r="B68" s="95" t="s">
         <v>851</v>
       </c>
-      <c r="C68" s="184" t="s">
+      <c r="C68" s="95" t="s">
         <v>435</v>
       </c>
-      <c r="D68" s="184" t="s">
+      <c r="D68" s="95" t="s">
         <v>434</v>
       </c>
-      <c r="E68" s="184" t="s">
+      <c r="E68" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F68" s="185">
+      <c r="F68" s="96">
         <v>6</v>
       </c>
-      <c r="G68" s="185">
+      <c r="G68" s="96">
         <v>4</v>
       </c>
-      <c r="H68" s="185">
+      <c r="H68" s="96">
         <v>0</v>
       </c>
-      <c r="I68" s="185">
+      <c r="I68" s="96">
         <v>10</v>
       </c>
-      <c r="J68" s="185">
+      <c r="J68" s="96">
         <v>10</v>
       </c>
-      <c r="K68" s="184" t="s">
+      <c r="K68" s="95" t="s">
         <v>954</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="60" x14ac:dyDescent="0.2">
-      <c r="A69" s="185">
+      <c r="A69" s="96">
         <v>49</v>
       </c>
-      <c r="B69" s="184" t="s">
+      <c r="B69" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="C69" s="184" t="s">
+      <c r="C69" s="95" t="s">
         <v>427</v>
       </c>
-      <c r="D69" s="184" t="s">
+      <c r="D69" s="95" t="s">
         <v>426</v>
       </c>
-      <c r="E69" s="184" t="s">
+      <c r="E69" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="F69" s="185">
+      <c r="F69" s="96">
         <v>6</v>
       </c>
-      <c r="G69" s="185">
+      <c r="G69" s="96">
         <v>0</v>
       </c>
-      <c r="H69" s="185">
+      <c r="H69" s="96">
         <v>4</v>
       </c>
-      <c r="I69" s="185">
+      <c r="I69" s="96">
         <v>10</v>
       </c>
-      <c r="J69" s="185">
+      <c r="J69" s="96">
         <v>10</v>
       </c>
-      <c r="K69" s="184" t="s">
+      <c r="K69" s="95" t="s">
         <v>962</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="185">
+      <c r="A70" s="96">
         <v>58</v>
       </c>
-      <c r="B70" s="184" t="s">
+      <c r="B70" s="95" t="s">
         <v>830</v>
       </c>
-      <c r="C70" s="184" t="s">
+      <c r="C70" s="95" t="s">
         <v>838</v>
       </c>
-      <c r="D70" s="184" t="s">
+      <c r="D70" s="95" t="s">
         <v>974</v>
       </c>
-      <c r="E70" s="184" t="s">
+      <c r="E70" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="F70" s="185">
+      <c r="F70" s="96">
         <v>0</v>
       </c>
-      <c r="G70" s="185">
+      <c r="G70" s="96">
         <v>10</v>
       </c>
-      <c r="H70" s="185">
+      <c r="H70" s="96">
         <v>0</v>
       </c>
-      <c r="I70" s="185">
+      <c r="I70" s="96">
         <v>10</v>
       </c>
-      <c r="J70" s="185">
+      <c r="J70" s="96">
         <v>10</v>
       </c>
-      <c r="K70" s="184" t="s">
+      <c r="K70" s="95" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="185">
+      <c r="A71" s="96">
         <v>13</v>
       </c>
-      <c r="B71" s="184" t="s">
+      <c r="B71" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="C71" s="184" t="s">
+      <c r="C71" s="95" t="s">
         <v>550</v>
       </c>
-      <c r="D71" s="184" t="s">
+      <c r="D71" s="95" t="s">
         <v>549</v>
       </c>
-      <c r="E71" s="184" t="s">
+      <c r="E71" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F71" s="185">
+      <c r="F71" s="96">
         <v>7</v>
       </c>
-      <c r="G71" s="185">
+      <c r="G71" s="96">
         <v>2</v>
       </c>
-      <c r="H71" s="185">
+      <c r="H71" s="96">
         <v>0</v>
       </c>
-      <c r="I71" s="185">
+      <c r="I71" s="96">
         <v>9</v>
       </c>
-      <c r="J71" s="185">
+      <c r="J71" s="96">
         <v>9</v>
       </c>
-      <c r="K71" s="184" t="s">
+      <c r="K71" s="95" t="s">
         <v>915</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="185">
+      <c r="A72" s="96">
         <v>41</v>
       </c>
-      <c r="B72" s="184" t="s">
+      <c r="B72" s="95" t="s">
         <v>826</v>
       </c>
-      <c r="C72" s="184" t="s">
+      <c r="C72" s="95" t="s">
         <v>210</v>
       </c>
-      <c r="D72" s="184" t="s">
+      <c r="D72" s="95" t="s">
         <v>947</v>
       </c>
-      <c r="E72" s="184" t="s">
+      <c r="E72" s="95" t="s">
         <v>847</v>
       </c>
-      <c r="F72" s="185">
+      <c r="F72" s="96">
         <v>0</v>
       </c>
-      <c r="G72" s="185">
+      <c r="G72" s="96">
         <v>8</v>
       </c>
-      <c r="H72" s="185">
+      <c r="H72" s="96">
         <v>1</v>
       </c>
-      <c r="I72" s="185">
+      <c r="I72" s="96">
         <v>9</v>
       </c>
-      <c r="J72" s="185">
+      <c r="J72" s="96">
         <v>9</v>
       </c>
-      <c r="K72" s="184" t="s">
+      <c r="K72" s="95" t="s">
         <v>948</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="90" x14ac:dyDescent="0.2">
-      <c r="A73" s="185">
+      <c r="A73" s="96">
         <v>48</v>
       </c>
-      <c r="B73" s="184" t="s">
+      <c r="B73" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="C73" s="184" t="s">
+      <c r="C73" s="95" t="s">
         <v>505</v>
       </c>
-      <c r="D73" s="184" t="s">
+      <c r="D73" s="95" t="s">
         <v>504</v>
       </c>
-      <c r="E73" s="184" t="s">
+      <c r="E73" s="95" t="s">
         <v>837</v>
       </c>
-      <c r="F73" s="185">
+      <c r="F73" s="96">
         <v>3</v>
       </c>
-      <c r="G73" s="185">
+      <c r="G73" s="96">
         <v>0</v>
       </c>
-      <c r="H73" s="185">
+      <c r="H73" s="96">
         <v>6</v>
       </c>
-      <c r="I73" s="185">
+      <c r="I73" s="96">
         <v>9</v>
       </c>
-      <c r="J73" s="185">
+      <c r="J73" s="96">
         <v>9</v>
       </c>
-      <c r="K73" s="184" t="s">
+      <c r="K73" s="95" t="s">
         <v>959</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="60" x14ac:dyDescent="0.2">
-      <c r="A74" s="185">
+      <c r="A74" s="96">
         <v>50</v>
       </c>
-      <c r="B74" s="184" t="s">
+      <c r="B74" s="95" t="s">
         <v>828</v>
       </c>
-      <c r="C74" s="184" t="s">
+      <c r="C74" s="95" t="s">
         <v>538</v>
       </c>
-      <c r="D74" s="184" t="s">
+      <c r="D74" s="95" t="s">
         <v>537</v>
       </c>
-      <c r="E74" s="184" t="s">
+      <c r="E74" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="F74" s="185">
+      <c r="F74" s="96">
         <v>6</v>
       </c>
-      <c r="G74" s="185">
+      <c r="G74" s="96">
         <v>0</v>
       </c>
-      <c r="H74" s="185">
+      <c r="H74" s="96">
         <v>3</v>
       </c>
-      <c r="I74" s="185">
+      <c r="I74" s="96">
         <v>9</v>
       </c>
-      <c r="J74" s="185">
+      <c r="J74" s="96">
         <v>9</v>
       </c>
-      <c r="K74" s="184" t="s">
+      <c r="K74" s="95" t="s">
         <v>963</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="185">
+      <c r="A75" s="96">
         <v>72</v>
       </c>
-      <c r="B75" s="184" t="s">
+      <c r="B75" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C75" s="184" t="s">
+      <c r="C75" s="95" t="s">
         <v>854</v>
       </c>
-      <c r="D75" s="184" t="s">
+      <c r="D75" s="95" t="s">
         <v>996</v>
       </c>
-      <c r="E75" s="184" t="s">
+      <c r="E75" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F75" s="185">
+      <c r="F75" s="96">
         <v>3</v>
       </c>
-      <c r="G75" s="185">
+      <c r="G75" s="96">
         <v>6</v>
       </c>
-      <c r="H75" s="185">
+      <c r="H75" s="96">
         <v>0</v>
       </c>
-      <c r="I75" s="185">
+      <c r="I75" s="96">
         <v>9</v>
       </c>
-      <c r="J75" s="185">
+      <c r="J75" s="96">
         <v>9</v>
       </c>
-      <c r="K75" s="184" t="s">
+      <c r="K75" s="95" t="s">
         <v>997</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="60" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="185">
+      <c r="A76" s="96">
         <v>73</v>
       </c>
-      <c r="B76" s="184" t="s">
+      <c r="B76" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C76" s="184" t="s">
+      <c r="C76" s="95" t="s">
         <v>858</v>
       </c>
-      <c r="D76" s="184" t="s">
+      <c r="D76" s="95" t="s">
         <v>998</v>
       </c>
-      <c r="E76" s="184" t="s">
+      <c r="E76" s="95" t="s">
         <v>827</v>
       </c>
-      <c r="F76" s="185">
+      <c r="F76" s="96">
         <v>3</v>
       </c>
-      <c r="G76" s="185">
+      <c r="G76" s="96">
         <v>6</v>
       </c>
-      <c r="H76" s="185">
+      <c r="H76" s="96">
         <v>0</v>
       </c>
-      <c r="I76" s="185">
+      <c r="I76" s="96">
         <v>9</v>
       </c>
-      <c r="J76" s="185">
+      <c r="J76" s="96">
         <v>9</v>
       </c>
-      <c r="K76" s="184" t="s">
+      <c r="K76" s="95" t="s">
         <v>999</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="45" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="185">
+      <c r="A77" s="96">
         <v>65</v>
       </c>
-      <c r="B77" s="184" t="s">
+      <c r="B77" s="95" t="s">
         <v>832</v>
       </c>
-      <c r="C77" s="184" t="s">
+      <c r="C77" s="95" t="s">
         <v>855</v>
       </c>
-      <c r="D77" s="184" t="s">
+      <c r="D77" s="95" t="s">
         <v>981</v>
       </c>
-      <c r="E77" s="184" t="s">
+      <c r="E77" s="95" t="s">
         <v>848</v>
       </c>
-      <c r="F77" s="185">
+      <c r="F77" s="96">
         <v>3</v>
       </c>
-      <c r="G77" s="185">
+      <c r="G77" s="96">
         <v>4</v>
       </c>
-      <c r="H77" s="185">
+      <c r="H77" s="96">
         <v>0</v>
       </c>
-      <c r="I77" s="185">
+      <c r="I77" s="96">
         <v>7</v>
       </c>
-      <c r="J77" s="185">
+      <c r="J77" s="96">
         <v>7</v>
       </c>
-      <c r="K77" s="184" t="s">
+      <c r="K77" s="95" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="45" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="185">
+      <c r="A78" s="96">
         <v>27</v>
       </c>
-      <c r="B78" s="184" t="s">
+      <c r="B78" s="95" t="s">
         <v>845</v>
       </c>
-      <c r="C78" s="184" t="s">
+      <c r="C78" s="95" t="s">
         <v>844</v>
       </c>
-      <c r="D78" s="184" t="s">
+      <c r="D78" s="95" t="s">
         <v>931</v>
       </c>
-      <c r="E78" s="184" t="s">
+      <c r="E78" s="95" t="s">
         <v>837</v>
       </c>
-      <c r="F78" s="185">
+      <c r="F78" s="96">
         <v>0</v>
       </c>
-      <c r="G78" s="185">
+      <c r="G78" s="96">
         <v>6</v>
       </c>
-      <c r="H78" s="185">
+      <c r="H78" s="96">
         <v>0</v>
       </c>
-      <c r="I78" s="185">
+      <c r="I78" s="96">
         <v>6</v>
       </c>
-      <c r="J78" s="185">
+      <c r="J78" s="96">
         <v>6</v>
       </c>
-      <c r="K78" s="184" t="s">
+      <c r="K78" s="95" t="s">
         <v>932</v>
       </c>
     </row>
@@ -58330,4 +58545,706 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4FE997C-E288-404B-9A58-D11E32C18C77}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" style="94" customWidth="1"/>
+    <col min="2" max="2" width="31.5" style="94" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="94" customWidth="1"/>
+    <col min="4" max="4" width="37.33203125" style="94" customWidth="1"/>
+    <col min="5" max="5" width="61.5" style="94" customWidth="1"/>
+    <col min="6" max="8" width="10.1640625" style="94" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="94" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="94" customWidth="1"/>
+    <col min="11" max="11" width="43" style="94" customWidth="1"/>
+    <col min="12" max="16384" width="14.5" style="94"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="189" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="190" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C1" s="190" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="190" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="190" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F1" s="190" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G1" s="190" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H1" s="190" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I1" s="190" t="s">
+        <v>1010</v>
+      </c>
+      <c r="J1" s="190" t="s">
+        <v>79</v>
+      </c>
+      <c r="K1" s="190" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="191">
+        <v>1</v>
+      </c>
+      <c r="B2" s="192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="192" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="192" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E2" s="192" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F2" s="193">
+        <v>5</v>
+      </c>
+      <c r="G2" s="193">
+        <v>0</v>
+      </c>
+      <c r="H2" s="193">
+        <v>5</v>
+      </c>
+      <c r="I2" s="193">
+        <v>0</v>
+      </c>
+      <c r="J2" s="193">
+        <v>2</v>
+      </c>
+      <c r="K2" s="192" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="105" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="191">
+        <v>2</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="192" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="192" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F3" s="193">
+        <v>10</v>
+      </c>
+      <c r="G3" s="193">
+        <v>0</v>
+      </c>
+      <c r="H3" s="193">
+        <v>10</v>
+      </c>
+      <c r="I3" s="193">
+        <v>0</v>
+      </c>
+      <c r="J3" s="193">
+        <v>2</v>
+      </c>
+      <c r="K3" s="192" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="191">
+        <v>3</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="192" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="192" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E4" s="192" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F4" s="193">
+        <v>21</v>
+      </c>
+      <c r="G4" s="193">
+        <v>0</v>
+      </c>
+      <c r="H4" s="193">
+        <v>21</v>
+      </c>
+      <c r="I4" s="193">
+        <v>0</v>
+      </c>
+      <c r="J4" s="193">
+        <v>2</v>
+      </c>
+      <c r="K4" s="192" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="191">
+        <v>4</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="192" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="192" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E5" s="192" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F5" s="193">
+        <v>21</v>
+      </c>
+      <c r="G5" s="193">
+        <v>0</v>
+      </c>
+      <c r="H5" s="193">
+        <v>21</v>
+      </c>
+      <c r="I5" s="193">
+        <v>0</v>
+      </c>
+      <c r="J5" s="193">
+        <v>2</v>
+      </c>
+      <c r="K5" s="192" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="191">
+        <v>5</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="192" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F6" s="193">
+        <v>4</v>
+      </c>
+      <c r="G6" s="193">
+        <v>0</v>
+      </c>
+      <c r="H6" s="193">
+        <v>4</v>
+      </c>
+      <c r="I6" s="193">
+        <v>0</v>
+      </c>
+      <c r="J6" s="193">
+        <v>2</v>
+      </c>
+      <c r="K6" s="192" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="191">
+        <v>6</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>196</v>
+      </c>
+      <c r="E7" s="192" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F7" s="193">
+        <v>4</v>
+      </c>
+      <c r="G7" s="193">
+        <v>0</v>
+      </c>
+      <c r="H7" s="193">
+        <v>4</v>
+      </c>
+      <c r="I7" s="193">
+        <v>0</v>
+      </c>
+      <c r="J7" s="193">
+        <v>2</v>
+      </c>
+      <c r="K7" s="192" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="191">
+        <v>7</v>
+      </c>
+      <c r="B8" s="192" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="192" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="192" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F8" s="193">
+        <v>1</v>
+      </c>
+      <c r="G8" s="193">
+        <v>0</v>
+      </c>
+      <c r="H8" s="193">
+        <v>1</v>
+      </c>
+      <c r="I8" s="193">
+        <v>0</v>
+      </c>
+      <c r="J8" s="193">
+        <v>2</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="191">
+        <v>8</v>
+      </c>
+      <c r="B9" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="192" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F9" s="193">
+        <v>1</v>
+      </c>
+      <c r="G9" s="193">
+        <v>0</v>
+      </c>
+      <c r="H9" s="193">
+        <v>1</v>
+      </c>
+      <c r="I9" s="193">
+        <v>0</v>
+      </c>
+      <c r="J9" s="193">
+        <v>2</v>
+      </c>
+      <c r="K9" s="192" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="191">
+        <v>9</v>
+      </c>
+      <c r="B10" s="192" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="192" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="192" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F10" s="193">
+        <v>12</v>
+      </c>
+      <c r="G10" s="193">
+        <v>0</v>
+      </c>
+      <c r="H10" s="193">
+        <v>12</v>
+      </c>
+      <c r="I10" s="193">
+        <v>0</v>
+      </c>
+      <c r="J10" s="193">
+        <v>2</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="191">
+        <v>10</v>
+      </c>
+      <c r="B11" s="192" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="192" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="192" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="192" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F11" s="193">
+        <v>10</v>
+      </c>
+      <c r="G11" s="193">
+        <v>0</v>
+      </c>
+      <c r="H11" s="193">
+        <v>10</v>
+      </c>
+      <c r="I11" s="193">
+        <v>0</v>
+      </c>
+      <c r="J11" s="193">
+        <v>2</v>
+      </c>
+      <c r="K11" s="192" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="135" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="191">
+        <v>11</v>
+      </c>
+      <c r="B12" s="192" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="192" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="192" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F12" s="193">
+        <v>11</v>
+      </c>
+      <c r="G12" s="193">
+        <v>0</v>
+      </c>
+      <c r="H12" s="193">
+        <v>11</v>
+      </c>
+      <c r="I12" s="193">
+        <v>0</v>
+      </c>
+      <c r="J12" s="193">
+        <v>2</v>
+      </c>
+      <c r="K12" s="192" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="191">
+        <v>12</v>
+      </c>
+      <c r="B13" s="192" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="192" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="192" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F13" s="193">
+        <v>4</v>
+      </c>
+      <c r="G13" s="193">
+        <v>0</v>
+      </c>
+      <c r="H13" s="193">
+        <v>4</v>
+      </c>
+      <c r="I13" s="193">
+        <v>0</v>
+      </c>
+      <c r="J13" s="193">
+        <v>2</v>
+      </c>
+      <c r="K13" s="192" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="191">
+        <v>13</v>
+      </c>
+      <c r="B14" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="192" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="192" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F14" s="193">
+        <v>3</v>
+      </c>
+      <c r="G14" s="193">
+        <v>0</v>
+      </c>
+      <c r="H14" s="193">
+        <v>3</v>
+      </c>
+      <c r="I14" s="193">
+        <v>0</v>
+      </c>
+      <c r="J14" s="193">
+        <v>2</v>
+      </c>
+      <c r="K14" s="192" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="191">
+        <v>14</v>
+      </c>
+      <c r="B15" s="192" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="192" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="192" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F15" s="193">
+        <v>2</v>
+      </c>
+      <c r="G15" s="193">
+        <v>0</v>
+      </c>
+      <c r="H15" s="193">
+        <v>2</v>
+      </c>
+      <c r="I15" s="193">
+        <v>0</v>
+      </c>
+      <c r="J15" s="193">
+        <v>2</v>
+      </c>
+      <c r="K15" s="192" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="191">
+        <v>15</v>
+      </c>
+      <c r="B16" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="192" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="192" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="192" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F16" s="193">
+        <v>1</v>
+      </c>
+      <c r="G16" s="193">
+        <v>0</v>
+      </c>
+      <c r="H16" s="193">
+        <v>1</v>
+      </c>
+      <c r="I16" s="193">
+        <v>0</v>
+      </c>
+      <c r="J16" s="193">
+        <v>2</v>
+      </c>
+      <c r="K16" s="192" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="191">
+        <v>16</v>
+      </c>
+      <c r="B17" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="192" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="192" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F17" s="193">
+        <v>1</v>
+      </c>
+      <c r="G17" s="193">
+        <v>0</v>
+      </c>
+      <c r="H17" s="193">
+        <v>1</v>
+      </c>
+      <c r="I17" s="193">
+        <v>0</v>
+      </c>
+      <c r="J17" s="193">
+        <v>2</v>
+      </c>
+      <c r="K17" s="192" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="191">
+        <v>17</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="192" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F18" s="193">
+        <v>1</v>
+      </c>
+      <c r="G18" s="193">
+        <v>0</v>
+      </c>
+      <c r="H18" s="193">
+        <v>1</v>
+      </c>
+      <c r="I18" s="193">
+        <v>0</v>
+      </c>
+      <c r="J18" s="193">
+        <v>2</v>
+      </c>
+      <c r="K18" s="192" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="194"/>
+      <c r="B19" s="195" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C19" s="195"/>
+      <c r="D19" s="195"/>
+      <c r="E19" s="195"/>
+      <c r="F19" s="190">
+        <v>112</v>
+      </c>
+      <c r="G19" s="190">
+        <v>0</v>
+      </c>
+      <c r="H19" s="190">
+        <v>112</v>
+      </c>
+      <c r="I19" s="190">
+        <v>0</v>
+      </c>
+      <c r="J19" s="190"/>
+      <c r="K19" s="195" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{625172B7-BDA4-7D4A-BF0F-873A050348EB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>